--- a/Flour_Frontier_Analysis_Workbook.xlsx
+++ b/Flour_Frontier_Analysis_Workbook.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://genmills-my.sharepoint.com/personal/jake_gilstein_genmills_com/Documents/Desktop/Website Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{5DE6A0F3-4851-4F23-AC15-357559DF3344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3F3AD2F-C041-43B4-9E64-832230CEB3A0}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="8_{5DE6A0F3-4851-4F23-AC15-357559DF3344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16BA550F-BCF3-45CF-BD66-0FADDEDEE710}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2112" uniqueCount="778">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2120" uniqueCount="786">
   <si>
     <t>50 Cities · 6 Weighted Lenses</t>
   </si>
@@ -2376,6 +2376,43 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Population projections are based on U.S. Census Bureau national population projection datasets, which forecast population by age, sex, race, Hispanic origin, and nativity through 2060.</t>
+  </si>
+  <si>
+    <t>https://www.census.gov/programs-surveys/popproj.html</t>
+  </si>
+  <si>
+    <t>https://www.statista.com/statistics/251238/hispanic-population-of-the-us/</t>
+  </si>
+  <si>
+    <t>Hispanic population CAGR was calculated from Statista’s U.S. Hispanic population forecast, which is based on U.S. Census Bureau projections</t>
+  </si>
+  <si>
+    <t>https://www.knowledge-sourcing.com/report/global-functional-flours-market#report-section-overview</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Functional flour demand is projected to grow at a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>6.17% CAGR over five years, from $52.37B in 2026 to $70.65B in 2031, supported by clean-label, plant-protein, gluten-free, and bakery formulation demand.</t>
+    </r>
+  </si>
+  <si>
+    <t>Index Metric Creation</t>
+  </si>
+  <si>
+    <t>Index shows whether we are over- or under-developed in a market compared to how big that market is. GMI Index = (GMI share of its own pounds in a metro ÷ that metro’s share of total industry pounds) × 100.                                                                                                                                                                                                                                                                                                           Example: If Houston makes up 4% of the total flour industry, but only 2% of GMI’s flour volume, then:
+2% ÷ 4% × 100 = 50
+So Houston would have a GMI Index of 50. That means GMI is only about halfway developed in Houston compared to the size of the market, which signals a strong opportunity.</t>
   </si>
 </sst>
 </file>
@@ -2385,7 +2422,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* \-??_);_(@_)"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2468,6 +2505,39 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -2541,11 +2611,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2608,8 +2679,23 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2627,8 +2713,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2712,9 +2799,16 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LensScores" displayName="LensScores" ref="A1:K51" totalsRowShown="0">
   <autoFilter ref="A1:K51" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K51">
+    <sortCondition descending="1" ref="G1:G51"/>
+  </sortState>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Overall Rank"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="City / Metro"/>
@@ -2752,6 +2846,9 @@
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="AllCityRanking" displayName="AllCityRanking" ref="A1:AD51" totalsRowShown="0">
   <autoFilter ref="A1:AD51" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AD51">
+    <sortCondition descending="1" ref="E1:E51"/>
+  </sortState>
   <tableColumns count="30">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Overall Rank"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="City / Metro"/>
@@ -3010,24 +3107,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="30" t="s">
         <v>777</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
     </row>
     <row r="2" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
     </row>
     <row r="3" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
@@ -3036,12 +3133,12 @@
       <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
+      <c r="C3" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
     </row>
     <row r="4" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
@@ -3050,12 +3147,12 @@
       <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
     </row>
     <row r="5" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
@@ -3064,12 +3161,12 @@
       <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
     </row>
     <row r="6" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
@@ -3078,12 +3175,12 @@
       <c r="B6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
@@ -3092,12 +3189,12 @@
       <c r="B7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="23"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
     </row>
     <row r="8" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
@@ -3106,12 +3203,12 @@
       <c r="B8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
     </row>
     <row r="9" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
@@ -3120,24 +3217,24 @@
       <c r="B9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
     </row>
     <row r="10" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="24"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="24" t="s">
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
@@ -3479,37 +3576,37 @@
     </row>
     <row r="3" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="9">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>56</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E3" s="11">
-        <v>3.95</v>
+        <v>4.99</v>
       </c>
       <c r="F3" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="G3" s="11">
+        <v>5</v>
+      </c>
+      <c r="H3" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="I3" s="11">
+        <v>1</v>
+      </c>
+      <c r="J3" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="K3" s="11">
         <v>4</v>
-      </c>
-      <c r="G3" s="11">
-        <v>2</v>
-      </c>
-      <c r="H3" s="11">
-        <v>5</v>
-      </c>
-      <c r="I3" s="11">
-        <v>4</v>
-      </c>
-      <c r="J3" s="11">
-        <v>5</v>
-      </c>
-      <c r="K3" s="11">
-        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
@@ -3549,92 +3646,92 @@
     </row>
     <row r="5" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="9">
+        <v>9</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="E5" s="11">
+        <v>4.76</v>
+      </c>
+      <c r="F5" s="11">
+        <v>2.6</v>
+      </c>
+      <c r="G5" s="11">
+        <v>5</v>
+      </c>
+      <c r="H5" s="11">
+        <v>3.8</v>
+      </c>
+      <c r="I5" s="11">
+        <v>1</v>
+      </c>
+      <c r="J5" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="K5" s="11">
         <v>4</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="E5" s="11">
-        <v>3.3</v>
-      </c>
-      <c r="F5" s="11">
-        <v>3</v>
-      </c>
-      <c r="G5" s="11">
-        <v>4</v>
-      </c>
-      <c r="H5" s="11">
-        <v>5</v>
-      </c>
-      <c r="I5" s="11">
-        <v>3</v>
-      </c>
-      <c r="J5" s="11">
-        <v>3</v>
-      </c>
-      <c r="K5" s="11">
-        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="9">
+        <v>10</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="11">
+        <v>4.6900000000000004</v>
+      </c>
+      <c r="F6" s="11">
+        <v>2.6</v>
+      </c>
+      <c r="G6" s="11">
         <v>5</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="E6" s="11">
-        <v>2.8</v>
-      </c>
-      <c r="F6" s="11">
+      <c r="H6" s="11">
+        <v>4.2</v>
+      </c>
+      <c r="I6" s="11">
         <v>1</v>
       </c>
-      <c r="G6" s="11">
-        <v>4</v>
-      </c>
-      <c r="H6" s="11">
-        <v>1</v>
-      </c>
-      <c r="I6" s="11">
-        <v>5</v>
-      </c>
       <c r="J6" s="11">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="K6" s="11">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="9">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="E7" s="11">
-        <v>4.99</v>
+        <v>4.6100000000000003</v>
       </c>
       <c r="F7" s="11">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="G7" s="11">
         <v>5</v>
@@ -3646,36 +3743,36 @@
         <v>1</v>
       </c>
       <c r="J7" s="11">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="K7" s="11">
-        <v>4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="9">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="E8" s="11">
-        <v>4.91</v>
+        <v>3.66</v>
       </c>
       <c r="F8" s="11">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="G8" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H8" s="11">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="I8" s="11">
         <v>1</v>
@@ -3684,33 +3781,33 @@
         <v>2.5</v>
       </c>
       <c r="K8" s="11">
-        <v>3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="9">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="E9" s="11">
-        <v>4.84</v>
+        <v>4.3899999999999997</v>
       </c>
       <c r="F9" s="11">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="G9" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H9" s="11">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I9" s="11">
         <v>1</v>
@@ -3724,28 +3821,28 @@
     </row>
     <row r="10" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="9">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E10" s="11">
-        <v>4.76</v>
+        <v>4.91</v>
       </c>
       <c r="F10" s="11">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="G10" s="11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H10" s="11">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="I10" s="11">
         <v>1</v>
@@ -3754,33 +3851,33 @@
         <v>2.5</v>
       </c>
       <c r="K10" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>56</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="E11" s="11">
-        <v>4.6900000000000004</v>
+        <v>4.84</v>
       </c>
       <c r="F11" s="11">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="G11" s="11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H11" s="11">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="I11" s="11">
         <v>1</v>
@@ -3789,33 +3886,33 @@
         <v>2.5</v>
       </c>
       <c r="K11" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="9">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E12" s="11">
-        <v>4.6100000000000003</v>
+        <v>3.9</v>
       </c>
       <c r="F12" s="11">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="G12" s="11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H12" s="11">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="I12" s="11">
         <v>1</v>
@@ -3829,28 +3926,28 @@
     </row>
     <row r="13" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="9">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="E13" s="11">
-        <v>4.54</v>
+        <v>4.24</v>
       </c>
       <c r="F13" s="11">
         <v>3</v>
       </c>
       <c r="G13" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H13" s="11">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="I13" s="11">
         <v>1</v>
@@ -3859,33 +3956,33 @@
         <v>2.5</v>
       </c>
       <c r="K13" s="11">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="9">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>56</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="E14" s="11">
-        <v>4.46</v>
+        <v>3.85</v>
       </c>
       <c r="F14" s="11">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="G14" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H14" s="11">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I14" s="11">
         <v>1</v>
@@ -3894,33 +3991,33 @@
         <v>2.5</v>
       </c>
       <c r="K14" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="9">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E15" s="11">
-        <v>4.3899999999999997</v>
+        <v>3.62</v>
       </c>
       <c r="F15" s="11">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="G15" s="11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H15" s="11">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="I15" s="11">
         <v>1</v>
@@ -3929,15 +4026,15 @@
         <v>2.5</v>
       </c>
       <c r="K15" s="11">
-        <v>4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="9">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>56</v>
@@ -3946,51 +4043,51 @@
         <v>63</v>
       </c>
       <c r="E16" s="11">
-        <v>4.3099999999999996</v>
+        <v>3.3</v>
       </c>
       <c r="F16" s="11">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="G16" s="11">
         <v>4</v>
       </c>
       <c r="H16" s="11">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="I16" s="11">
+        <v>3</v>
+      </c>
+      <c r="J16" s="11">
+        <v>3</v>
+      </c>
+      <c r="K16" s="11">
         <v>1</v>
-      </c>
-      <c r="J16" s="11">
-        <v>2.5</v>
-      </c>
-      <c r="K16" s="11">
-        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>56</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E17" s="11">
-        <v>4.24</v>
+        <v>4.3099999999999996</v>
       </c>
       <c r="F17" s="11">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="G17" s="11">
         <v>4</v>
       </c>
       <c r="H17" s="11">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="I17" s="11">
         <v>1</v>
@@ -3999,50 +4096,50 @@
         <v>2.5</v>
       </c>
       <c r="K17" s="11">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="9">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="E18" s="11">
-        <v>4.16</v>
+        <v>2.99</v>
       </c>
       <c r="F18" s="11">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="G18" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H18" s="11">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="I18" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J18" s="11">
         <v>3.5</v>
       </c>
       <c r="K18" s="11">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" s="9">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>65</v>
@@ -4051,45 +4148,45 @@
         <v>66</v>
       </c>
       <c r="E19" s="11">
-        <v>4.09</v>
+        <v>2.8</v>
       </c>
       <c r="F19" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G19" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H19" s="11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I19" s="11">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J19" s="11">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="K19" s="11">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="9">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>56</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E20" s="11">
-        <v>4.01</v>
+        <v>4.46</v>
       </c>
       <c r="F20" s="11">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="G20" s="11">
         <v>3</v>
@@ -4101,62 +4198,62 @@
         <v>1</v>
       </c>
       <c r="J20" s="11">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="K20" s="11">
-        <v>3.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A21" s="9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>65</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="E21" s="11">
-        <v>3.99</v>
+        <v>3.94</v>
       </c>
       <c r="F21" s="11">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="G21" s="11">
         <v>3</v>
       </c>
       <c r="H21" s="11">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="I21" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J21" s="11">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="K21" s="11">
-        <v>5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" s="9">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>65</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="E22" s="11">
-        <v>3.94</v>
+        <v>3.43</v>
       </c>
       <c r="F22" s="11">
         <v>3.6</v>
@@ -4165,7 +4262,7 @@
         <v>3</v>
       </c>
       <c r="H22" s="11">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I22" s="11">
         <v>1</v>
@@ -4174,39 +4271,39 @@
         <v>2.5</v>
       </c>
       <c r="K22" s="11">
-        <v>4.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" s="9">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E23" s="11">
-        <v>3.9</v>
+        <v>2.79</v>
       </c>
       <c r="F23" s="11">
         <v>3.5</v>
       </c>
       <c r="G23" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H23" s="11">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="I23" s="11">
         <v>1</v>
       </c>
       <c r="J23" s="11">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="K23" s="11">
         <v>2.5</v>
@@ -4214,28 +4311,28 @@
     </row>
     <row r="24" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" s="9">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="E24" s="11">
-        <v>3.85</v>
+        <v>4.54</v>
       </c>
       <c r="F24" s="11">
         <v>3</v>
       </c>
       <c r="G24" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H24" s="11">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="I24" s="11">
         <v>1</v>
@@ -4244,24 +4341,24 @@
         <v>2.5</v>
       </c>
       <c r="K24" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="9">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>65</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="E25" s="11">
-        <v>3.8</v>
+        <v>4.16</v>
       </c>
       <c r="F25" s="11">
         <v>3</v>
@@ -4270,33 +4367,33 @@
         <v>3</v>
       </c>
       <c r="H25" s="11">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="I25" s="11">
+        <v>1</v>
+      </c>
+      <c r="J25" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="K25" s="11">
         <v>2</v>
-      </c>
-      <c r="J25" s="11">
-        <v>2.5</v>
-      </c>
-      <c r="K25" s="11">
-        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="9">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E26" s="11">
-        <v>3.76</v>
+        <v>4.09</v>
       </c>
       <c r="F26" s="11">
         <v>3</v>
@@ -4305,7 +4402,7 @@
         <v>3</v>
       </c>
       <c r="H26" s="11">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="I26" s="11">
         <v>1</v>
@@ -4314,24 +4411,24 @@
         <v>2.5</v>
       </c>
       <c r="K26" s="11">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="9">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="E27" s="11">
-        <v>3.71</v>
+        <v>4.01</v>
       </c>
       <c r="F27" s="11">
         <v>3</v>
@@ -4340,103 +4437,103 @@
         <v>3</v>
       </c>
       <c r="H27" s="11">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="I27" s="11">
         <v>1</v>
       </c>
       <c r="J27" s="11">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="K27" s="11">
-        <v>5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" s="9">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="E28" s="11">
-        <v>3.66</v>
+        <v>3.99</v>
       </c>
       <c r="F28" s="11">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="G28" s="11">
+        <v>3</v>
+      </c>
+      <c r="H28" s="11">
+        <v>3.8</v>
+      </c>
+      <c r="I28" s="11">
+        <v>2</v>
+      </c>
+      <c r="J28" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="K28" s="11">
         <v>5</v>
-      </c>
-      <c r="H28" s="11">
-        <v>4.2</v>
-      </c>
-      <c r="I28" s="11">
-        <v>1</v>
-      </c>
-      <c r="J28" s="11">
-        <v>2.5</v>
-      </c>
-      <c r="K28" s="11">
-        <v>2.5</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" s="9">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="E29" s="11">
-        <v>3.62</v>
+        <v>3.8</v>
       </c>
       <c r="F29" s="11">
         <v>3</v>
       </c>
       <c r="G29" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H29" s="11">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="I29" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="11">
         <v>2.5</v>
       </c>
       <c r="K29" s="11">
-        <v>2.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" s="9">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="E30" s="11">
-        <v>3.57</v>
+        <v>3.76</v>
       </c>
       <c r="F30" s="11">
         <v>3</v>
@@ -4445,13 +4542,13 @@
         <v>3</v>
       </c>
       <c r="H30" s="11">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="I30" s="11">
         <v>1</v>
       </c>
       <c r="J30" s="11">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="K30" s="11">
         <v>5</v>
@@ -4459,19 +4556,19 @@
     </row>
     <row r="31" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="9">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="E31" s="11">
-        <v>3.52</v>
+        <v>3.71</v>
       </c>
       <c r="F31" s="11">
         <v>3</v>
@@ -4480,7 +4577,7 @@
         <v>3</v>
       </c>
       <c r="H31" s="11">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I31" s="11">
         <v>1</v>
@@ -4494,10 +4591,10 @@
     </row>
     <row r="32" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="9">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C32" s="9" t="s">
         <v>65</v>
@@ -4506,7 +4603,7 @@
         <v>78</v>
       </c>
       <c r="E32" s="11">
-        <v>3.48</v>
+        <v>3.57</v>
       </c>
       <c r="F32" s="11">
         <v>3</v>
@@ -4515,42 +4612,42 @@
         <v>3</v>
       </c>
       <c r="H32" s="11">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="I32" s="11">
         <v>1</v>
       </c>
       <c r="J32" s="11">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="K32" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="9">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="E33" s="11">
-        <v>3.43</v>
+        <v>3.52</v>
       </c>
       <c r="F33" s="11">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="G33" s="11">
         <v>3</v>
       </c>
       <c r="H33" s="11">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="I33" s="11">
         <v>1</v>
@@ -4559,24 +4656,24 @@
         <v>2.5</v>
       </c>
       <c r="K33" s="11">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="9">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>65</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="E34" s="11">
-        <v>3.38</v>
+        <v>3.48</v>
       </c>
       <c r="F34" s="11">
         <v>3</v>
@@ -4585,7 +4682,7 @@
         <v>3</v>
       </c>
       <c r="H34" s="11">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="I34" s="11">
         <v>1</v>
@@ -4594,24 +4691,24 @@
         <v>3.5</v>
       </c>
       <c r="K34" s="11">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A35" s="9">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="E35" s="11">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="F35" s="11">
         <v>3</v>
@@ -4620,42 +4717,42 @@
         <v>3</v>
       </c>
       <c r="H35" s="11">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="I35" s="11">
         <v>1</v>
       </c>
       <c r="J35" s="11">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="K35" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" s="9">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C36" s="9" t="s">
         <v>56</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E36" s="11">
-        <v>3.29</v>
+        <v>3.34</v>
       </c>
       <c r="F36" s="11">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="G36" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H36" s="11">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="I36" s="11">
         <v>1</v>
@@ -4739,34 +4836,34 @@
     </row>
     <row r="39" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39" s="9">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>107</v>
+        <v>58</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="E39" s="11">
-        <v>3.15</v>
+        <v>3.95</v>
       </c>
       <c r="F39" s="11">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="G39" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H39" s="11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I39" s="11">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J39" s="11">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="K39" s="11">
         <v>5</v>
@@ -4774,28 +4871,28 @@
     </row>
     <row r="40" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A40" s="9">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>69</v>
+        <v>116</v>
       </c>
       <c r="E40" s="11">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="F40" s="11">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="G40" s="11">
         <v>2</v>
       </c>
       <c r="H40" s="11">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="I40" s="11">
         <v>1</v>
@@ -4804,33 +4901,33 @@
         <v>2.5</v>
       </c>
       <c r="K40" s="11">
-        <v>2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" s="9">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E41" s="11">
-        <v>3.06</v>
+        <v>2.6</v>
       </c>
       <c r="F41" s="11">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="G41" s="11">
         <v>2</v>
       </c>
       <c r="H41" s="11">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="I41" s="11">
         <v>1</v>
@@ -4839,33 +4936,33 @@
         <v>2.5</v>
       </c>
       <c r="K41" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A42" s="9">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="E42" s="11">
-        <v>3.01</v>
+        <v>2.21</v>
       </c>
       <c r="F42" s="11">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="G42" s="11">
         <v>2</v>
       </c>
       <c r="H42" s="11">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="I42" s="11">
         <v>1</v>
@@ -4874,103 +4971,103 @@
         <v>2.5</v>
       </c>
       <c r="K42" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A43" s="9">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>113</v>
+        <v>71</v>
       </c>
       <c r="E43" s="11">
-        <v>2.99</v>
+        <v>3.29</v>
       </c>
       <c r="F43" s="11">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="G43" s="11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H43" s="11">
         <v>4</v>
       </c>
       <c r="I43" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J43" s="11">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="K43" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A44" s="9">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="E44" s="11">
-        <v>2.79</v>
+        <v>3.1</v>
       </c>
       <c r="F44" s="11">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="G44" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H44" s="11">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="I44" s="11">
         <v>1</v>
       </c>
       <c r="J44" s="11">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="K44" s="11">
-        <v>2.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A45" s="9">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="E45" s="11">
+        <v>3.06</v>
+      </c>
+      <c r="F45" s="11">
         <v>2.6</v>
-      </c>
-      <c r="F45" s="11">
-        <v>3.6</v>
       </c>
       <c r="G45" s="11">
         <v>2</v>
       </c>
       <c r="H45" s="11">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="I45" s="11">
         <v>1</v>
@@ -4979,33 +5076,33 @@
         <v>2.5</v>
       </c>
       <c r="K45" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A46" s="9">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>116</v>
+        <v>76</v>
       </c>
       <c r="E46" s="11">
-        <v>2.4</v>
+        <v>3.01</v>
       </c>
       <c r="F46" s="11">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="G46" s="11">
         <v>2</v>
       </c>
       <c r="H46" s="11">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="I46" s="11">
         <v>1</v>
@@ -5014,15 +5111,15 @@
         <v>2.5</v>
       </c>
       <c r="K46" s="11">
-        <v>2.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A47" s="9">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C47" s="9" t="s">
         <v>81</v>
@@ -5031,16 +5128,16 @@
         <v>110</v>
       </c>
       <c r="E47" s="11">
-        <v>2.21</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="F47" s="11">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="G47" s="11">
         <v>2</v>
       </c>
       <c r="H47" s="11">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="I47" s="11">
         <v>1</v>
@@ -5049,33 +5146,33 @@
         <v>2.5</v>
       </c>
       <c r="K47" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A48" s="9">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C48" s="9" t="s">
         <v>81</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="E48" s="11">
-        <v>2.0099999999999998</v>
+        <v>1.99</v>
       </c>
       <c r="F48" s="11">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="G48" s="11">
         <v>2</v>
       </c>
       <c r="H48" s="11">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="I48" s="11">
         <v>1</v>
@@ -5084,33 +5181,33 @@
         <v>2.5</v>
       </c>
       <c r="K48" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A49" s="9">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E49" s="11">
-        <v>1.99</v>
+        <v>1.5</v>
       </c>
       <c r="F49" s="11">
+        <v>3.6</v>
+      </c>
+      <c r="G49" s="11">
+        <v>1</v>
+      </c>
+      <c r="H49" s="11">
         <v>2.5</v>
-      </c>
-      <c r="G49" s="11">
-        <v>2</v>
-      </c>
-      <c r="H49" s="11">
-        <v>4</v>
       </c>
       <c r="I49" s="11">
         <v>1</v>
@@ -5119,33 +5216,33 @@
         <v>2.5</v>
       </c>
       <c r="K49" s="11">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A50" s="9">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="C50" s="9" t="s">
         <v>73</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E50" s="11">
-        <v>1.5</v>
+        <v>3.15</v>
       </c>
       <c r="F50" s="11">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="G50" s="11">
         <v>1</v>
       </c>
       <c r="H50" s="11">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="I50" s="11">
         <v>1</v>
@@ -5154,7 +5251,7 @@
         <v>2.5</v>
       </c>
       <c r="K50" s="11">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
@@ -7193,46 +7290,44 @@
         <v>128</v>
       </c>
     </row>
-    <row r="2" spans="1:30" ht="31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:30" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A2" s="9">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="E2" s="11">
-        <v>4.3499999999999996</v>
+        <v>4.99</v>
       </c>
       <c r="F2" s="11">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="G2" s="11">
         <v>5</v>
       </c>
       <c r="H2" s="11">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I2" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J2" s="11">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K2" s="11">
         <v>4</v>
       </c>
       <c r="L2" s="11">
-        <v>5</v>
-      </c>
-      <c r="M2" s="9">
-        <v>1</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="M2" s="9"/>
       <c r="N2" s="9" t="s">
         <v>56</v>
       </c>
@@ -7243,422 +7338,426 @@
         <v>57</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>197</v>
+        <v>237</v>
       </c>
       <c r="R2" s="9" t="s">
-        <v>198</v>
+        <v>238</v>
       </c>
       <c r="S2" s="9" t="s">
-        <v>199</v>
+        <v>239</v>
       </c>
       <c r="T2" s="9" t="s">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="U2" s="9" t="s">
-        <v>201</v>
+        <v>241</v>
       </c>
       <c r="V2" s="9" t="s">
-        <v>202</v>
+        <v>242</v>
       </c>
       <c r="W2" s="9" t="s">
-        <v>203</v>
+        <v>243</v>
       </c>
       <c r="X2" s="9" t="s">
-        <v>204</v>
+        <v>244</v>
       </c>
       <c r="Y2" s="16">
-        <v>60315422</v>
+        <v>25188081</v>
       </c>
       <c r="Z2" s="17">
-        <v>8768572</v>
+        <v>5929072</v>
       </c>
       <c r="AA2" s="18">
-        <v>0.14499999999999999</v>
+        <v>0.23499999999999999</v>
       </c>
       <c r="AB2" s="18">
-        <v>1.4999999999999999E-2</v>
+        <v>0.16300000000000001</v>
       </c>
       <c r="AC2" s="9">
-        <v>48.7</v>
+        <v>75</v>
       </c>
       <c r="AD2" s="9" t="s">
-        <v>131</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3" spans="1:30" ht="31" x14ac:dyDescent="0.35">
       <c r="A3" s="9">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="E3" s="11">
-        <v>3.95</v>
+        <v>4.91</v>
       </c>
       <c r="F3" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="G3" s="11">
         <v>4</v>
       </c>
-      <c r="G3" s="11">
-        <v>2</v>
-      </c>
       <c r="H3" s="11">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="I3" s="11">
+        <v>1</v>
+      </c>
+      <c r="J3" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="K3" s="11">
+        <v>3</v>
+      </c>
+      <c r="L3" s="11">
         <v>4</v>
       </c>
-      <c r="J3" s="11">
-        <v>5</v>
-      </c>
-      <c r="K3" s="11">
-        <v>5</v>
-      </c>
-      <c r="L3" s="11">
-        <v>5</v>
-      </c>
-      <c r="M3" s="9">
-        <v>2</v>
-      </c>
+      <c r="M3" s="9"/>
       <c r="N3" s="9" t="s">
         <v>56</v>
       </c>
       <c r="O3" s="9" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="P3" s="9" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="Q3" s="9" t="s">
-        <v>205</v>
+        <v>245</v>
       </c>
       <c r="R3" s="9" t="s">
-        <v>206</v>
+        <v>246</v>
       </c>
       <c r="S3" s="9" t="s">
-        <v>207</v>
+        <v>247</v>
       </c>
       <c r="T3" s="9" t="s">
-        <v>208</v>
+        <v>248</v>
       </c>
       <c r="U3" s="9" t="s">
-        <v>209</v>
+        <v>249</v>
       </c>
       <c r="V3" s="9" t="s">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="W3" s="9" t="s">
-        <v>211</v>
+        <v>251</v>
       </c>
       <c r="X3" s="9" t="s">
-        <v>212</v>
+        <v>252</v>
       </c>
       <c r="Y3" s="16">
-        <v>49767388</v>
+        <v>12199521</v>
       </c>
       <c r="Z3" s="17">
-        <v>10166816</v>
+        <v>2959394</v>
       </c>
       <c r="AA3" s="18">
-        <v>0.20399999999999999</v>
-      </c>
-      <c r="AB3" s="19">
-        <v>5.2999999999999999E-2</v>
+        <v>0.24299999999999999</v>
+      </c>
+      <c r="AB3" s="18">
+        <v>5.5E-2</v>
       </c>
       <c r="AC3" s="9">
-        <v>65</v>
+        <v>76.599999999999994</v>
       </c>
       <c r="AD3" s="9" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="4" spans="1:30" ht="46.5" x14ac:dyDescent="0.35">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30" ht="31" x14ac:dyDescent="0.35">
       <c r="A4" s="9">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="E4" s="11">
+        <v>4.84</v>
+      </c>
+      <c r="F4" s="11">
         <v>3.5</v>
       </c>
-      <c r="F4" s="11">
-        <v>3</v>
-      </c>
       <c r="G4" s="11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H4" s="11">
         <v>4</v>
       </c>
       <c r="I4" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4" s="11">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="K4" s="11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L4" s="11">
-        <v>5</v>
-      </c>
-      <c r="M4" s="9">
-        <v>3</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="M4" s="9"/>
       <c r="N4" s="9" t="s">
         <v>56</v>
       </c>
       <c r="O4" s="9" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="P4" s="9" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="Q4" s="9" t="s">
-        <v>214</v>
+        <v>253</v>
       </c>
       <c r="R4" s="9" t="s">
-        <v>215</v>
+        <v>254</v>
       </c>
       <c r="S4" s="9" t="s">
-        <v>216</v>
+        <v>255</v>
       </c>
       <c r="T4" s="9" t="s">
-        <v>217</v>
+        <v>256</v>
       </c>
       <c r="U4" s="9" t="s">
-        <v>218</v>
+        <v>257</v>
       </c>
       <c r="V4" s="9" t="s">
-        <v>219</v>
+        <v>258</v>
       </c>
       <c r="W4" s="9" t="s">
-        <v>220</v>
+        <v>259</v>
       </c>
       <c r="X4" s="9" t="s">
-        <v>221</v>
+        <v>260</v>
       </c>
       <c r="Y4" s="16">
-        <v>36774911</v>
+        <v>12931762</v>
       </c>
       <c r="Z4" s="17">
-        <v>8769191</v>
+        <v>2663849</v>
       </c>
       <c r="AA4" s="18">
-        <v>0.23799999999999999</v>
+        <v>0.20599999999999999</v>
       </c>
       <c r="AB4" s="18">
-        <v>-1.4999999999999999E-2</v>
+        <v>8.2000000000000003E-2</v>
       </c>
       <c r="AC4" s="9">
-        <v>79.900000000000006</v>
+        <v>64.5</v>
       </c>
       <c r="AD4" s="9" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="5" spans="1:30" ht="46.5" x14ac:dyDescent="0.35">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" ht="31" x14ac:dyDescent="0.35">
       <c r="A5" s="9">
+        <v>9</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="E5" s="11">
+        <v>4.76</v>
+      </c>
+      <c r="F5" s="11">
+        <v>2.6</v>
+      </c>
+      <c r="G5" s="11">
+        <v>5</v>
+      </c>
+      <c r="H5" s="11">
+        <v>3.8</v>
+      </c>
+      <c r="I5" s="11">
+        <v>1</v>
+      </c>
+      <c r="J5" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="K5" s="11">
         <v>4</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="E5" s="11">
-        <v>3.3</v>
-      </c>
-      <c r="F5" s="11">
-        <v>3</v>
-      </c>
-      <c r="G5" s="11">
+      <c r="L5" s="11">
         <v>4</v>
       </c>
-      <c r="H5" s="11">
-        <v>5</v>
-      </c>
-      <c r="I5" s="11">
-        <v>3</v>
-      </c>
-      <c r="J5" s="11">
-        <v>3</v>
-      </c>
-      <c r="K5" s="11">
-        <v>1</v>
-      </c>
-      <c r="L5" s="11">
-        <v>5</v>
-      </c>
-      <c r="M5" s="9">
-        <v>4</v>
-      </c>
+      <c r="M5" s="9"/>
       <c r="N5" s="9" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="O5" s="9" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="P5" s="9" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="Q5" s="9" t="s">
-        <v>222</v>
+        <v>261</v>
       </c>
       <c r="R5" s="9" t="s">
-        <v>223</v>
+        <v>262</v>
       </c>
       <c r="S5" s="9" t="s">
-        <v>224</v>
+        <v>263</v>
       </c>
       <c r="T5" s="9" t="s">
-        <v>225</v>
+        <v>264</v>
       </c>
       <c r="U5" s="9" t="s">
-        <v>226</v>
+        <v>265</v>
       </c>
       <c r="V5" s="9" t="s">
-        <v>227</v>
+        <v>266</v>
       </c>
       <c r="W5" s="9" t="s">
-        <v>228</v>
+        <v>267</v>
       </c>
       <c r="X5" s="9" t="s">
-        <v>229</v>
+        <v>268</v>
       </c>
       <c r="Y5" s="16">
-        <v>34502075</v>
+        <v>9025740</v>
       </c>
       <c r="Z5" s="17">
-        <v>9975811</v>
+        <v>3341881</v>
       </c>
       <c r="AA5" s="18">
-        <v>0.28899999999999998</v>
+        <v>0.37</v>
       </c>
       <c r="AB5" s="18">
-        <v>0.13900000000000001</v>
+        <v>0.21099999999999999</v>
       </c>
       <c r="AC5" s="9">
-        <v>101.1</v>
+        <v>121.6</v>
       </c>
       <c r="AD5" s="9" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" spans="1:30" ht="31" x14ac:dyDescent="0.35">
       <c r="A6" s="9">
+        <v>10</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="E6" s="11">
+        <v>4.6900000000000004</v>
+      </c>
+      <c r="F6" s="11">
+        <v>2.6</v>
+      </c>
+      <c r="G6" s="11">
         <v>5</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="E6" s="11">
-        <v>2.8</v>
-      </c>
-      <c r="F6" s="11">
+      <c r="H6" s="11">
+        <v>4.2</v>
+      </c>
+      <c r="I6" s="11">
         <v>1</v>
       </c>
-      <c r="G6" s="11">
+      <c r="J6" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="K6" s="11">
+        <v>3</v>
+      </c>
+      <c r="L6" s="11">
         <v>4</v>
       </c>
-      <c r="H6" s="11">
-        <v>1</v>
-      </c>
-      <c r="I6" s="11">
-        <v>5</v>
-      </c>
-      <c r="J6" s="11">
-        <v>3</v>
-      </c>
-      <c r="K6" s="11">
-        <v>5</v>
-      </c>
-      <c r="L6" s="11">
-        <v>5</v>
-      </c>
-      <c r="M6" s="9">
-        <v>5</v>
-      </c>
+      <c r="M6" s="9"/>
       <c r="N6" s="9" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="O6" s="9" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="P6" s="9" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="Q6" s="9" t="s">
-        <v>230</v>
+        <v>269</v>
       </c>
       <c r="R6" s="9" t="s">
-        <v>231</v>
+        <v>270</v>
       </c>
       <c r="S6" s="9" t="s">
-        <v>232</v>
+        <v>271</v>
       </c>
       <c r="T6" s="9" t="s">
-        <v>233</v>
+        <v>272</v>
       </c>
       <c r="U6" s="9" t="s">
-        <v>234</v>
+        <v>273</v>
       </c>
       <c r="V6" s="9" t="s">
-        <v>235</v>
+        <v>274</v>
       </c>
       <c r="W6" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="16"/>
-      <c r="Z6" s="17"/>
-      <c r="AA6" s="9"/>
-      <c r="AB6" s="9"/>
-      <c r="AC6" s="9"/>
+        <v>275</v>
+      </c>
+      <c r="X6" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="Y6" s="16">
+        <v>9970288</v>
+      </c>
+      <c r="Z6" s="17">
+        <v>3849052</v>
+      </c>
+      <c r="AA6" s="18">
+        <v>0.38600000000000001</v>
+      </c>
+      <c r="AB6" s="18">
+        <v>0.18099999999999999</v>
+      </c>
+      <c r="AC6" s="9">
+        <v>130.69999999999999</v>
+      </c>
       <c r="AD6" s="9" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A7" s="9">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="E7" s="11">
-        <v>4.99</v>
+        <v>4.6100000000000003</v>
       </c>
       <c r="F7" s="11">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="G7" s="11">
         <v>5</v>
@@ -7670,73 +7769,73 @@
         <v>1</v>
       </c>
       <c r="J7" s="11">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="K7" s="11">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="L7" s="11">
         <v>4</v>
       </c>
       <c r="M7" s="9"/>
       <c r="N7" s="9" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="O7" s="9" t="s">
         <v>196</v>
       </c>
       <c r="P7" s="9" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="Q7" s="9" t="s">
-        <v>237</v>
+        <v>277</v>
       </c>
       <c r="R7" s="9" t="s">
-        <v>238</v>
+        <v>278</v>
       </c>
       <c r="S7" s="9" t="s">
-        <v>239</v>
+        <v>279</v>
       </c>
       <c r="T7" s="9" t="s">
-        <v>240</v>
+        <v>280</v>
       </c>
       <c r="U7" s="9" t="s">
-        <v>241</v>
+        <v>281</v>
       </c>
       <c r="V7" s="9" t="s">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="W7" s="9" t="s">
-        <v>243</v>
+        <v>282</v>
       </c>
       <c r="X7" s="9" t="s">
-        <v>244</v>
+        <v>75</v>
       </c>
       <c r="Y7" s="16">
-        <v>25188081</v>
+        <v>8968538</v>
       </c>
       <c r="Z7" s="17">
-        <v>5929072</v>
+        <v>2250705</v>
       </c>
       <c r="AA7" s="18">
-        <v>0.23499999999999999</v>
+        <v>0.251</v>
       </c>
       <c r="AB7" s="18">
-        <v>0.16300000000000001</v>
+        <v>0.14099999999999999</v>
       </c>
       <c r="AC7" s="9">
-        <v>75</v>
+        <v>143.9</v>
       </c>
       <c r="AD7" s="9" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30" ht="31" x14ac:dyDescent="0.35">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A8" s="9">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>140</v>
@@ -7745,16 +7844,16 @@
         <v>141</v>
       </c>
       <c r="E8" s="11">
-        <v>4.91</v>
+        <v>4.54</v>
       </c>
       <c r="F8" s="11">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="G8" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H8" s="11">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="I8" s="11">
         <v>1</v>
@@ -7763,70 +7862,58 @@
         <v>2.5</v>
       </c>
       <c r="K8" s="11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L8" s="11">
         <v>4</v>
       </c>
       <c r="M8" s="9"/>
       <c r="N8" s="9" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="O8" s="9" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="P8" s="9" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="Q8" s="9" t="s">
-        <v>245</v>
+        <v>283</v>
       </c>
       <c r="R8" s="9" t="s">
-        <v>246</v>
+        <v>284</v>
       </c>
       <c r="S8" s="9" t="s">
-        <v>247</v>
+        <v>285</v>
       </c>
       <c r="T8" s="9" t="s">
-        <v>248</v>
+        <v>286</v>
       </c>
       <c r="U8" s="9" t="s">
-        <v>249</v>
+        <v>287</v>
       </c>
       <c r="V8" s="9" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="W8" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="X8" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="Y8" s="16">
-        <v>12199521</v>
-      </c>
-      <c r="Z8" s="17">
-        <v>2959394</v>
-      </c>
-      <c r="AA8" s="18">
-        <v>0.24299999999999999</v>
-      </c>
-      <c r="AB8" s="18">
-        <v>5.5E-2</v>
-      </c>
-      <c r="AC8" s="9">
-        <v>76.599999999999994</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="X8" s="9"/>
+      <c r="Y8" s="16"/>
+      <c r="Z8" s="17"/>
+      <c r="AA8" s="9"/>
+      <c r="AB8" s="9"/>
+      <c r="AC8" s="9"/>
       <c r="AD8" s="9" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="9" spans="1:30" ht="31" x14ac:dyDescent="0.35">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A9" s="9">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>140</v>
@@ -7835,13 +7922,13 @@
         <v>141</v>
       </c>
       <c r="E9" s="11">
-        <v>4.84</v>
+        <v>4.46</v>
       </c>
       <c r="F9" s="11">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="G9" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H9" s="11">
         <v>4</v>
@@ -7853,7 +7940,7 @@
         <v>2.5</v>
       </c>
       <c r="K9" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L9" s="11">
         <v>4</v>
@@ -7866,57 +7953,57 @@
         <v>196</v>
       </c>
       <c r="P9" s="9" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="Q9" s="9" t="s">
-        <v>253</v>
+        <v>290</v>
       </c>
       <c r="R9" s="9" t="s">
-        <v>254</v>
+        <v>291</v>
       </c>
       <c r="S9" s="9" t="s">
-        <v>255</v>
+        <v>292</v>
       </c>
       <c r="T9" s="9" t="s">
-        <v>256</v>
+        <v>293</v>
       </c>
       <c r="U9" s="9" t="s">
-        <v>257</v>
+        <v>294</v>
       </c>
       <c r="V9" s="9" t="s">
-        <v>258</v>
+        <v>202</v>
       </c>
       <c r="W9" s="9" t="s">
-        <v>259</v>
+        <v>295</v>
       </c>
       <c r="X9" s="9" t="s">
-        <v>260</v>
+        <v>296</v>
       </c>
       <c r="Y9" s="16">
-        <v>12931762</v>
+        <v>6360244</v>
       </c>
       <c r="Z9" s="17">
-        <v>2663849</v>
+        <v>1759953</v>
       </c>
       <c r="AA9" s="18">
-        <v>0.20599999999999999</v>
+        <v>0.27700000000000002</v>
       </c>
       <c r="AB9" s="18">
-        <v>8.2000000000000003E-2</v>
+        <v>0.13900000000000001</v>
       </c>
       <c r="AC9" s="9">
-        <v>64.5</v>
+        <v>119.5</v>
       </c>
       <c r="AD9" s="9" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="10" spans="1:30" ht="31" x14ac:dyDescent="0.35">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A10" s="9">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>140</v>
@@ -7925,16 +8012,16 @@
         <v>143</v>
       </c>
       <c r="E10" s="11">
-        <v>4.76</v>
+        <v>4.3899999999999997</v>
       </c>
       <c r="F10" s="11">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="G10" s="11">
         <v>5</v>
       </c>
       <c r="H10" s="11">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="I10" s="11">
         <v>1</v>
@@ -7950,171 +8037,173 @@
       </c>
       <c r="M10" s="9"/>
       <c r="N10" s="9" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="O10" s="9" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="P10" s="9" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="Q10" s="9" t="s">
-        <v>261</v>
+        <v>297</v>
       </c>
       <c r="R10" s="9" t="s">
-        <v>262</v>
+        <v>298</v>
       </c>
       <c r="S10" s="9" t="s">
-        <v>263</v>
+        <v>299</v>
       </c>
       <c r="T10" s="9" t="s">
-        <v>264</v>
+        <v>300</v>
       </c>
       <c r="U10" s="9" t="s">
-        <v>265</v>
+        <v>301</v>
       </c>
       <c r="V10" s="9" t="s">
-        <v>266</v>
+        <v>302</v>
       </c>
       <c r="W10" s="9" t="s">
-        <v>267</v>
+        <v>303</v>
       </c>
       <c r="X10" s="9" t="s">
-        <v>268</v>
+        <v>304</v>
       </c>
       <c r="Y10" s="16">
-        <v>9025740</v>
+        <v>7007976</v>
       </c>
       <c r="Z10" s="17">
-        <v>3341881</v>
+        <v>1384666</v>
       </c>
       <c r="AA10" s="18">
-        <v>0.37</v>
+        <v>0.19800000000000001</v>
       </c>
       <c r="AB10" s="18">
-        <v>0.21099999999999999</v>
+        <v>7.9000000000000001E-2</v>
       </c>
       <c r="AC10" s="9">
-        <v>121.6</v>
+        <v>86.1</v>
       </c>
       <c r="AD10" s="9" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="31" x14ac:dyDescent="0.35">
       <c r="A11" s="9">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="E11" s="11">
-        <v>4.6900000000000004</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="F11" s="11">
-        <v>2.6</v>
+        <v>5</v>
       </c>
       <c r="G11" s="11">
         <v>5</v>
       </c>
       <c r="H11" s="11">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="I11" s="11">
+        <v>3</v>
+      </c>
+      <c r="J11" s="11">
+        <v>4</v>
+      </c>
+      <c r="K11" s="11">
+        <v>4</v>
+      </c>
+      <c r="L11" s="11">
+        <v>5</v>
+      </c>
+      <c r="M11" s="9">
         <v>1</v>
       </c>
-      <c r="J11" s="11">
-        <v>2.5</v>
-      </c>
-      <c r="K11" s="11">
-        <v>3</v>
-      </c>
-      <c r="L11" s="11">
-        <v>4</v>
-      </c>
-      <c r="M11" s="9"/>
       <c r="N11" s="9" t="s">
         <v>56</v>
       </c>
       <c r="O11" s="9" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="P11" s="9" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="Q11" s="9" t="s">
-        <v>269</v>
+        <v>197</v>
       </c>
       <c r="R11" s="9" t="s">
-        <v>270</v>
+        <v>198</v>
       </c>
       <c r="S11" s="9" t="s">
-        <v>271</v>
+        <v>199</v>
       </c>
       <c r="T11" s="9" t="s">
-        <v>272</v>
+        <v>200</v>
       </c>
       <c r="U11" s="9" t="s">
-        <v>273</v>
+        <v>201</v>
       </c>
       <c r="V11" s="9" t="s">
-        <v>274</v>
+        <v>202</v>
       </c>
       <c r="W11" s="9" t="s">
-        <v>275</v>
+        <v>203</v>
       </c>
       <c r="X11" s="9" t="s">
-        <v>276</v>
+        <v>204</v>
       </c>
       <c r="Y11" s="16">
-        <v>9970288</v>
+        <v>60315422</v>
       </c>
       <c r="Z11" s="17">
-        <v>3849052</v>
+        <v>8768572</v>
       </c>
       <c r="AA11" s="18">
-        <v>0.38600000000000001</v>
+        <v>0.14499999999999999</v>
       </c>
       <c r="AB11" s="18">
-        <v>0.18099999999999999</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="AC11" s="9">
-        <v>130.69999999999999</v>
+        <v>48.7</v>
       </c>
       <c r="AD11" s="9" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A12" s="9">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>140</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E12" s="11">
-        <v>4.6100000000000003</v>
+        <v>4.3099999999999996</v>
       </c>
       <c r="F12" s="11">
         <v>2.6</v>
       </c>
       <c r="G12" s="11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H12" s="11">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="I12" s="11">
         <v>1</v>
@@ -8123,70 +8212,58 @@
         <v>2.5</v>
       </c>
       <c r="K12" s="11">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="L12" s="11">
         <v>4</v>
       </c>
       <c r="M12" s="9"/>
       <c r="N12" s="9" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="O12" s="9" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="P12" s="9" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="Q12" s="9" t="s">
-        <v>277</v>
+        <v>305</v>
       </c>
       <c r="R12" s="9" t="s">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="S12" s="9" t="s">
-        <v>279</v>
+        <v>307</v>
       </c>
       <c r="T12" s="9" t="s">
-        <v>280</v>
+        <v>308</v>
       </c>
       <c r="U12" s="9" t="s">
-        <v>281</v>
+        <v>309</v>
       </c>
       <c r="V12" s="9" t="s">
-        <v>258</v>
+        <v>210</v>
       </c>
       <c r="W12" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="X12" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="Y12" s="16">
-        <v>8968538</v>
-      </c>
-      <c r="Z12" s="17">
-        <v>2250705</v>
-      </c>
-      <c r="AA12" s="18">
-        <v>0.251</v>
-      </c>
-      <c r="AB12" s="18">
-        <v>0.14099999999999999</v>
-      </c>
-      <c r="AC12" s="9">
-        <v>143.9</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="16"/>
+      <c r="Z12" s="17"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
       <c r="AD12" s="9" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="13" spans="1:30" ht="46.5" x14ac:dyDescent="0.35">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" ht="31" x14ac:dyDescent="0.35">
       <c r="A13" s="9">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>140</v>
@@ -8195,16 +8272,16 @@
         <v>141</v>
       </c>
       <c r="E13" s="11">
-        <v>4.54</v>
+        <v>4.24</v>
       </c>
       <c r="F13" s="11">
         <v>3</v>
       </c>
       <c r="G13" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H13" s="11">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="I13" s="11">
         <v>1</v>
@@ -8213,41 +8290,41 @@
         <v>2.5</v>
       </c>
       <c r="K13" s="11">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L13" s="11">
         <v>4</v>
       </c>
       <c r="M13" s="9"/>
       <c r="N13" s="9" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="P13" s="9" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="Q13" s="9" t="s">
-        <v>283</v>
+        <v>311</v>
       </c>
       <c r="R13" s="9" t="s">
-        <v>284</v>
+        <v>312</v>
       </c>
       <c r="S13" s="9" t="s">
-        <v>285</v>
+        <v>313</v>
       </c>
       <c r="T13" s="9" t="s">
-        <v>286</v>
+        <v>314</v>
       </c>
       <c r="U13" s="9" t="s">
-        <v>287</v>
+        <v>315</v>
       </c>
       <c r="V13" s="9" t="s">
-        <v>258</v>
+        <v>316</v>
       </c>
       <c r="W13" s="9" t="s">
-        <v>288</v>
+        <v>317</v>
       </c>
       <c r="X13" s="9"/>
       <c r="Y13" s="16"/>
@@ -8256,15 +8333,15 @@
       <c r="AB13" s="9"/>
       <c r="AC13" s="9"/>
       <c r="AD13" s="9" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="14" spans="1:30" ht="46.5" x14ac:dyDescent="0.35">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" ht="31" x14ac:dyDescent="0.35">
       <c r="A14" s="9">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>140</v>
@@ -8273,106 +8350,106 @@
         <v>141</v>
       </c>
       <c r="E14" s="11">
-        <v>4.46</v>
+        <v>4.16</v>
       </c>
       <c r="F14" s="11">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="G14" s="11">
         <v>3</v>
       </c>
       <c r="H14" s="11">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I14" s="11">
         <v>1</v>
       </c>
       <c r="J14" s="11">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="K14" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L14" s="11">
         <v>4</v>
       </c>
       <c r="M14" s="9"/>
       <c r="N14" s="9" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="O14" s="9" t="s">
         <v>196</v>
       </c>
       <c r="P14" s="9" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="Q14" s="9" t="s">
-        <v>290</v>
+        <v>319</v>
       </c>
       <c r="R14" s="9" t="s">
-        <v>291</v>
+        <v>320</v>
       </c>
       <c r="S14" s="9" t="s">
-        <v>292</v>
+        <v>321</v>
       </c>
       <c r="T14" s="9" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="U14" s="9" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="V14" s="9" t="s">
-        <v>202</v>
+        <v>274</v>
       </c>
       <c r="W14" s="9" t="s">
-        <v>295</v>
+        <v>322</v>
       </c>
       <c r="X14" s="9" t="s">
-        <v>296</v>
+        <v>323</v>
       </c>
       <c r="Y14" s="16">
-        <v>6360244</v>
+        <v>8262973</v>
       </c>
       <c r="Z14" s="17">
-        <v>1759953</v>
+        <v>647539</v>
       </c>
       <c r="AA14" s="18">
-        <v>0.27700000000000002</v>
+        <v>7.8E-2</v>
       </c>
       <c r="AB14" s="18">
-        <v>0.13900000000000001</v>
+        <v>-4.2000000000000003E-2</v>
       </c>
       <c r="AC14" s="9">
-        <v>119.5</v>
+        <v>26.3</v>
       </c>
       <c r="AD14" s="9" t="s">
-        <v>147</v>
+        <v>324</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A15" s="9">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>140</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E15" s="11">
-        <v>4.3899999999999997</v>
+        <v>4.09</v>
       </c>
       <c r="F15" s="11">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="G15" s="11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H15" s="11">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="I15" s="11">
         <v>1</v>
@@ -8381,70 +8458,70 @@
         <v>2.5</v>
       </c>
       <c r="K15" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L15" s="11">
         <v>4</v>
       </c>
       <c r="M15" s="9"/>
       <c r="N15" s="9" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="O15" s="9" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="Q15" s="9" t="s">
-        <v>297</v>
+        <v>325</v>
       </c>
       <c r="R15" s="9" t="s">
-        <v>298</v>
+        <v>326</v>
       </c>
       <c r="S15" s="9" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="T15" s="9" t="s">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="U15" s="9" t="s">
-        <v>301</v>
+        <v>287</v>
       </c>
       <c r="V15" s="9" t="s">
-        <v>302</v>
+        <v>328</v>
       </c>
       <c r="W15" s="9" t="s">
-        <v>303</v>
+        <v>329</v>
       </c>
       <c r="X15" s="9" t="s">
-        <v>304</v>
+        <v>330</v>
       </c>
       <c r="Y15" s="16">
-        <v>7007976</v>
+        <v>42944984</v>
       </c>
       <c r="Z15" s="17">
-        <v>1384666</v>
+        <v>9888300</v>
       </c>
       <c r="AA15" s="18">
-        <v>0.19800000000000001</v>
+        <v>0.23</v>
       </c>
       <c r="AB15" s="18">
-        <v>7.9000000000000001E-2</v>
+        <v>-1.0999999999999999E-2</v>
       </c>
       <c r="AC15" s="9">
-        <v>86.1</v>
+        <v>102</v>
       </c>
       <c r="AD15" s="9" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="16" spans="1:30" ht="46.5" x14ac:dyDescent="0.35">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" ht="31" x14ac:dyDescent="0.35">
       <c r="A16" s="9">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>140</v>
@@ -8453,25 +8530,25 @@
         <v>141</v>
       </c>
       <c r="E16" s="11">
-        <v>4.3099999999999996</v>
+        <v>4.01</v>
       </c>
       <c r="F16" s="11">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="G16" s="11">
+        <v>3</v>
+      </c>
+      <c r="H16" s="11">
         <v>4</v>
-      </c>
-      <c r="H16" s="11">
-        <v>3.8</v>
       </c>
       <c r="I16" s="11">
         <v>1</v>
       </c>
       <c r="J16" s="11">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="K16" s="11">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="L16" s="11">
         <v>4</v>
@@ -8484,106 +8561,118 @@
         <v>213</v>
       </c>
       <c r="P16" s="9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="Q16" s="9" t="s">
-        <v>305</v>
+        <v>332</v>
       </c>
       <c r="R16" s="9" t="s">
-        <v>306</v>
+        <v>333</v>
       </c>
       <c r="S16" s="9" t="s">
-        <v>307</v>
+        <v>334</v>
       </c>
       <c r="T16" s="9" t="s">
-        <v>308</v>
+        <v>335</v>
       </c>
       <c r="U16" s="9" t="s">
-        <v>309</v>
+        <v>336</v>
       </c>
       <c r="V16" s="9" t="s">
-        <v>210</v>
+        <v>337</v>
       </c>
       <c r="W16" s="9" t="s">
-        <v>310</v>
-      </c>
-      <c r="X16" s="9"/>
-      <c r="Y16" s="16"/>
-      <c r="Z16" s="17"/>
-      <c r="AA16" s="9"/>
-      <c r="AB16" s="9"/>
-      <c r="AC16" s="9"/>
+        <v>338</v>
+      </c>
+      <c r="X16" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="Y16" s="16">
+        <v>6280324</v>
+      </c>
+      <c r="Z16" s="17">
+        <v>1731421</v>
+      </c>
+      <c r="AA16" s="18">
+        <v>0.27600000000000002</v>
+      </c>
+      <c r="AB16" s="18">
+        <v>-8.9999999999999993E-3</v>
+      </c>
+      <c r="AC16" s="9">
+        <v>92.9</v>
+      </c>
       <c r="AD16" s="9" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="31" x14ac:dyDescent="0.35">
       <c r="A17" s="9">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>140</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E17" s="11">
-        <v>4.24</v>
+        <v>3.99</v>
       </c>
       <c r="F17" s="11">
         <v>3</v>
       </c>
       <c r="G17" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H17" s="11">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="I17" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J17" s="11">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="K17" s="11">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L17" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M17" s="9"/>
       <c r="N17" s="9" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="O17" s="9" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="Q17" s="9" t="s">
-        <v>311</v>
+        <v>340</v>
       </c>
       <c r="R17" s="9" t="s">
-        <v>312</v>
+        <v>341</v>
       </c>
       <c r="S17" s="9" t="s">
-        <v>313</v>
+        <v>342</v>
       </c>
       <c r="T17" s="9" t="s">
-        <v>314</v>
+        <v>286</v>
       </c>
       <c r="U17" s="9" t="s">
-        <v>315</v>
+        <v>287</v>
       </c>
       <c r="V17" s="9" t="s">
-        <v>316</v>
+        <v>343</v>
       </c>
       <c r="W17" s="9" t="s">
-        <v>317</v>
+        <v>344</v>
       </c>
       <c r="X17" s="9"/>
       <c r="Y17" s="16"/>
@@ -8592,105 +8681,107 @@
       <c r="AB17" s="9"/>
       <c r="AC17" s="9"/>
       <c r="AD17" s="9" t="s">
-        <v>318</v>
+        <v>171</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="31" x14ac:dyDescent="0.35">
       <c r="A18" s="9">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="E18" s="11">
-        <v>4.16</v>
+        <v>3.95</v>
       </c>
       <c r="F18" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G18" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H18" s="11">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="I18" s="11">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J18" s="11">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="K18" s="11">
+        <v>5</v>
+      </c>
+      <c r="L18" s="11">
+        <v>5</v>
+      </c>
+      <c r="M18" s="9">
         <v>2</v>
       </c>
-      <c r="L18" s="11">
-        <v>4</v>
-      </c>
-      <c r="M18" s="9"/>
       <c r="N18" s="9" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="O18" s="9" t="s">
         <v>196</v>
       </c>
       <c r="P18" s="9" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="Q18" s="9" t="s">
-        <v>319</v>
+        <v>205</v>
       </c>
       <c r="R18" s="9" t="s">
-        <v>320</v>
+        <v>206</v>
       </c>
       <c r="S18" s="9" t="s">
-        <v>321</v>
+        <v>207</v>
       </c>
       <c r="T18" s="9" t="s">
-        <v>286</v>
+        <v>208</v>
       </c>
       <c r="U18" s="9" t="s">
-        <v>287</v>
+        <v>209</v>
       </c>
       <c r="V18" s="9" t="s">
-        <v>274</v>
+        <v>210</v>
       </c>
       <c r="W18" s="9" t="s">
-        <v>322</v>
+        <v>211</v>
       </c>
       <c r="X18" s="9" t="s">
-        <v>323</v>
+        <v>212</v>
       </c>
       <c r="Y18" s="16">
-        <v>8262973</v>
+        <v>49767388</v>
       </c>
       <c r="Z18" s="17">
-        <v>647539</v>
+        <v>10166816</v>
       </c>
       <c r="AA18" s="18">
-        <v>7.8E-2</v>
-      </c>
-      <c r="AB18" s="18">
-        <v>-4.2000000000000003E-2</v>
+        <v>0.20399999999999999</v>
+      </c>
+      <c r="AB18" s="19">
+        <v>5.2999999999999999E-2</v>
       </c>
       <c r="AC18" s="9">
-        <v>26.3</v>
+        <v>65</v>
       </c>
       <c r="AD18" s="9" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="19" spans="1:30" ht="46.5" x14ac:dyDescent="0.35">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30" ht="31" x14ac:dyDescent="0.35">
       <c r="A19" s="9">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>140</v>
@@ -8699,10 +8790,10 @@
         <v>141</v>
       </c>
       <c r="E19" s="11">
-        <v>4.09</v>
+        <v>3.94</v>
       </c>
       <c r="F19" s="11">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="G19" s="11">
         <v>3</v>
@@ -8717,10 +8808,10 @@
         <v>2.5</v>
       </c>
       <c r="K19" s="11">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="L19" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M19" s="9"/>
       <c r="N19" s="9" t="s">
@@ -8733,54 +8824,42 @@
         <v>66</v>
       </c>
       <c r="Q19" s="9" t="s">
-        <v>325</v>
+        <v>345</v>
       </c>
       <c r="R19" s="9" t="s">
-        <v>326</v>
+        <v>346</v>
       </c>
       <c r="S19" s="9" t="s">
-        <v>327</v>
+        <v>347</v>
       </c>
       <c r="T19" s="9" t="s">
-        <v>286</v>
+        <v>348</v>
       </c>
       <c r="U19" s="9" t="s">
-        <v>287</v>
+        <v>349</v>
       </c>
       <c r="V19" s="9" t="s">
         <v>328</v>
       </c>
       <c r="W19" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="X19" s="9" t="s">
-        <v>330</v>
-      </c>
-      <c r="Y19" s="16">
-        <v>42944984</v>
-      </c>
-      <c r="Z19" s="17">
-        <v>9888300</v>
-      </c>
-      <c r="AA19" s="18">
-        <v>0.23</v>
-      </c>
-      <c r="AB19" s="18">
-        <v>-1.0999999999999999E-2</v>
-      </c>
-      <c r="AC19" s="9">
-        <v>102</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="X19" s="9"/>
+      <c r="Y19" s="16"/>
+      <c r="Z19" s="17"/>
+      <c r="AA19" s="9"/>
+      <c r="AB19" s="9"/>
+      <c r="AC19" s="9"/>
       <c r="AD19" s="9" t="s">
-        <v>331</v>
+        <v>148</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="31" x14ac:dyDescent="0.35">
       <c r="A20" s="9">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>140</v>
@@ -8789,88 +8868,88 @@
         <v>141</v>
       </c>
       <c r="E20" s="11">
-        <v>4.01</v>
+        <v>3.9</v>
       </c>
       <c r="F20" s="11">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="G20" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H20" s="11">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I20" s="11">
         <v>1</v>
       </c>
       <c r="J20" s="11">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="K20" s="11">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="L20" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M20" s="9"/>
       <c r="N20" s="9" t="s">
         <v>56</v>
       </c>
       <c r="O20" s="9" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="P20" s="9" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="Q20" s="9" t="s">
-        <v>332</v>
+        <v>351</v>
       </c>
       <c r="R20" s="9" t="s">
-        <v>333</v>
+        <v>352</v>
       </c>
       <c r="S20" s="9" t="s">
-        <v>334</v>
+        <v>353</v>
       </c>
       <c r="T20" s="9" t="s">
-        <v>335</v>
+        <v>354</v>
       </c>
       <c r="U20" s="9" t="s">
-        <v>336</v>
+        <v>355</v>
       </c>
       <c r="V20" s="9" t="s">
-        <v>337</v>
+        <v>356</v>
       </c>
       <c r="W20" s="9" t="s">
-        <v>338</v>
+        <v>357</v>
       </c>
       <c r="X20" s="9" t="s">
-        <v>339</v>
+        <v>358</v>
       </c>
       <c r="Y20" s="16">
-        <v>6280324</v>
+        <v>7278132</v>
       </c>
       <c r="Z20" s="17">
-        <v>1731421</v>
+        <v>1701711</v>
       </c>
       <c r="AA20" s="18">
-        <v>0.27600000000000002</v>
+        <v>0.23400000000000001</v>
       </c>
       <c r="AB20" s="18">
-        <v>-8.9999999999999993E-3</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="AC20" s="9">
-        <v>92.9</v>
+        <v>76</v>
       </c>
       <c r="AD20" s="9" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="21" spans="1:30" ht="31" x14ac:dyDescent="0.35">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="21" spans="1:30" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A21" s="9">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>140</v>
@@ -8879,103 +8958,115 @@
         <v>143</v>
       </c>
       <c r="E21" s="11">
-        <v>3.99</v>
+        <v>3.85</v>
       </c>
       <c r="F21" s="11">
         <v>3</v>
       </c>
       <c r="G21" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H21" s="11">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="I21" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J21" s="11">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="K21" s="11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L21" s="11">
         <v>3</v>
       </c>
       <c r="M21" s="9"/>
       <c r="N21" s="9" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="Q21" s="9" t="s">
-        <v>340</v>
+        <v>359</v>
       </c>
       <c r="R21" s="9" t="s">
-        <v>341</v>
+        <v>360</v>
       </c>
       <c r="S21" s="9" t="s">
-        <v>342</v>
+        <v>361</v>
       </c>
       <c r="T21" s="9" t="s">
-        <v>286</v>
+        <v>362</v>
       </c>
       <c r="U21" s="9" t="s">
-        <v>287</v>
+        <v>363</v>
       </c>
       <c r="V21" s="9" t="s">
-        <v>343</v>
+        <v>364</v>
       </c>
       <c r="W21" s="9" t="s">
-        <v>344</v>
-      </c>
-      <c r="X21" s="9"/>
-      <c r="Y21" s="16"/>
-      <c r="Z21" s="17"/>
-      <c r="AA21" s="9"/>
-      <c r="AB21" s="9"/>
-      <c r="AC21" s="9"/>
+        <v>365</v>
+      </c>
+      <c r="X21" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="Y21" s="16">
+        <v>40166336</v>
+      </c>
+      <c r="Z21" s="17">
+        <v>12477651</v>
+      </c>
+      <c r="AA21" s="18">
+        <v>0.311</v>
+      </c>
+      <c r="AB21" s="18">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="AC21" s="9">
+        <v>101.9</v>
+      </c>
       <c r="AD21" s="9" t="s">
-        <v>171</v>
+        <v>367</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="31" x14ac:dyDescent="0.35">
       <c r="A22" s="9">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>140</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E22" s="11">
-        <v>3.94</v>
+        <v>3.8</v>
       </c>
       <c r="F22" s="11">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="G22" s="11">
         <v>3</v>
       </c>
       <c r="H22" s="11">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="I22" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J22" s="11">
         <v>2.5</v>
       </c>
       <c r="K22" s="11">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="L22" s="11">
         <v>3</v>
@@ -8988,28 +9079,28 @@
         <v>196</v>
       </c>
       <c r="P22" s="9" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="Q22" s="9" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="R22" s="9" t="s">
-        <v>346</v>
+        <v>369</v>
       </c>
       <c r="S22" s="9" t="s">
-        <v>347</v>
+        <v>370</v>
       </c>
       <c r="T22" s="9" t="s">
-        <v>348</v>
+        <v>286</v>
       </c>
       <c r="U22" s="9" t="s">
-        <v>349</v>
+        <v>287</v>
       </c>
       <c r="V22" s="9" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="W22" s="9" t="s">
-        <v>350</v>
+        <v>371</v>
       </c>
       <c r="X22" s="9"/>
       <c r="Y22" s="16"/>
@@ -9018,15 +9109,15 @@
       <c r="AB22" s="9"/>
       <c r="AC22" s="9"/>
       <c r="AD22" s="9" t="s">
-        <v>148</v>
+        <v>174</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="31" x14ac:dyDescent="0.35">
       <c r="A23" s="9">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C23" s="9" t="s">
         <v>140</v>
@@ -9035,16 +9126,16 @@
         <v>141</v>
       </c>
       <c r="E23" s="11">
-        <v>3.9</v>
+        <v>3.76</v>
       </c>
       <c r="F23" s="11">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="G23" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H23" s="11">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="I23" s="11">
         <v>1</v>
@@ -9053,88 +9144,88 @@
         <v>2.5</v>
       </c>
       <c r="K23" s="11">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="L23" s="11">
         <v>3</v>
       </c>
       <c r="M23" s="9"/>
       <c r="N23" s="9" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="Q23" s="9" t="s">
-        <v>351</v>
+        <v>372</v>
       </c>
       <c r="R23" s="9" t="s">
-        <v>352</v>
+        <v>373</v>
       </c>
       <c r="S23" s="9" t="s">
-        <v>353</v>
+        <v>374</v>
       </c>
       <c r="T23" s="9" t="s">
-        <v>354</v>
+        <v>375</v>
       </c>
       <c r="U23" s="9" t="s">
-        <v>355</v>
+        <v>376</v>
       </c>
       <c r="V23" s="9" t="s">
-        <v>356</v>
+        <v>302</v>
       </c>
       <c r="W23" s="9" t="s">
-        <v>357</v>
+        <v>377</v>
       </c>
       <c r="X23" s="9" t="s">
-        <v>358</v>
+        <v>378</v>
       </c>
       <c r="Y23" s="16">
-        <v>7278132</v>
+        <v>54576044</v>
       </c>
       <c r="Z23" s="17">
-        <v>1701711</v>
+        <v>17491111</v>
       </c>
       <c r="AA23" s="18">
-        <v>0.23400000000000001</v>
+        <v>0.32</v>
       </c>
       <c r="AB23" s="18">
-        <v>4.8000000000000001E-2</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="AC23" s="9">
-        <v>76</v>
+        <v>103.8</v>
       </c>
       <c r="AD23" s="9" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="24" spans="1:30" ht="46.5" x14ac:dyDescent="0.35">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30" ht="31" x14ac:dyDescent="0.35">
       <c r="A24" s="9">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>140</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E24" s="11">
-        <v>3.85</v>
+        <v>3.71</v>
       </c>
       <c r="F24" s="11">
         <v>3</v>
       </c>
       <c r="G24" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H24" s="11">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="I24" s="11">
         <v>1</v>
@@ -9143,70 +9234,70 @@
         <v>2.5</v>
       </c>
       <c r="K24" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L24" s="11">
         <v>3</v>
       </c>
       <c r="M24" s="9"/>
       <c r="N24" s="9" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="O24" s="9" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="P24" s="9" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="Q24" s="9" t="s">
-        <v>359</v>
+        <v>379</v>
       </c>
       <c r="R24" s="9" t="s">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="S24" s="9" t="s">
-        <v>361</v>
+        <v>381</v>
       </c>
       <c r="T24" s="9" t="s">
-        <v>362</v>
+        <v>286</v>
       </c>
       <c r="U24" s="9" t="s">
-        <v>363</v>
+        <v>287</v>
       </c>
       <c r="V24" s="9" t="s">
-        <v>364</v>
+        <v>250</v>
       </c>
       <c r="W24" s="9" t="s">
-        <v>365</v>
+        <v>382</v>
       </c>
       <c r="X24" s="9" t="s">
-        <v>366</v>
+        <v>383</v>
       </c>
       <c r="Y24" s="16">
-        <v>40166336</v>
+        <v>25999310</v>
       </c>
       <c r="Z24" s="17">
-        <v>12477651</v>
+        <v>4612764</v>
       </c>
       <c r="AA24" s="18">
-        <v>0.311</v>
+        <v>0.17699999999999999</v>
       </c>
       <c r="AB24" s="18">
-        <v>5.7000000000000002E-2</v>
+        <v>3.1E-2</v>
       </c>
       <c r="AC24" s="9">
-        <v>101.9</v>
+        <v>56.1</v>
       </c>
       <c r="AD24" s="9" t="s">
-        <v>367</v>
+        <v>384</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="31" x14ac:dyDescent="0.35">
       <c r="A25" s="9">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>140</v>
@@ -9215,76 +9306,88 @@
         <v>143</v>
       </c>
       <c r="E25" s="11">
-        <v>3.8</v>
+        <v>3.66</v>
       </c>
       <c r="F25" s="11">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="G25" s="11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H25" s="11">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="I25" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J25" s="11">
         <v>2.5</v>
       </c>
       <c r="K25" s="11">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="L25" s="11">
         <v>3</v>
       </c>
       <c r="M25" s="9"/>
       <c r="N25" s="9" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="O25" s="9" t="s">
         <v>196</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="Q25" s="9" t="s">
-        <v>368</v>
+        <v>385</v>
       </c>
       <c r="R25" s="9" t="s">
-        <v>369</v>
+        <v>386</v>
       </c>
       <c r="S25" s="9" t="s">
-        <v>370</v>
+        <v>387</v>
       </c>
       <c r="T25" s="9" t="s">
-        <v>286</v>
+        <v>388</v>
       </c>
       <c r="U25" s="9" t="s">
-        <v>287</v>
+        <v>389</v>
       </c>
       <c r="V25" s="9" t="s">
-        <v>343</v>
+        <v>390</v>
       </c>
       <c r="W25" s="9" t="s">
-        <v>371</v>
-      </c>
-      <c r="X25" s="9"/>
-      <c r="Y25" s="16"/>
-      <c r="Z25" s="17"/>
-      <c r="AA25" s="9"/>
-      <c r="AB25" s="9"/>
-      <c r="AC25" s="9"/>
+        <v>391</v>
+      </c>
+      <c r="X25" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="Y25" s="16">
+        <v>7718796</v>
+      </c>
+      <c r="Z25" s="17">
+        <v>3186892</v>
+      </c>
+      <c r="AA25" s="18">
+        <v>0.41299999999999998</v>
+      </c>
+      <c r="AB25" s="18">
+        <v>0.14699999999999999</v>
+      </c>
+      <c r="AC25" s="9">
+        <v>154.69999999999999</v>
+      </c>
       <c r="AD25" s="9" t="s">
-        <v>174</v>
+        <v>393</v>
       </c>
     </row>
     <row r="26" spans="1:30" ht="31" x14ac:dyDescent="0.35">
       <c r="A26" s="9">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>140</v>
@@ -9293,13 +9396,13 @@
         <v>141</v>
       </c>
       <c r="E26" s="11">
-        <v>3.76</v>
+        <v>3.62</v>
       </c>
       <c r="F26" s="11">
         <v>3</v>
       </c>
       <c r="G26" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H26" s="11">
         <v>4.5</v>
@@ -9311,70 +9414,58 @@
         <v>2.5</v>
       </c>
       <c r="K26" s="11">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="L26" s="11">
         <v>3</v>
       </c>
       <c r="M26" s="9"/>
       <c r="N26" s="9" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="O26" s="9" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="P26" s="9" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="Q26" s="9" t="s">
-        <v>372</v>
+        <v>394</v>
       </c>
       <c r="R26" s="9" t="s">
-        <v>373</v>
+        <v>395</v>
       </c>
       <c r="S26" s="9" t="s">
-        <v>374</v>
+        <v>396</v>
       </c>
       <c r="T26" s="9" t="s">
-        <v>375</v>
+        <v>397</v>
       </c>
       <c r="U26" s="9" t="s">
-        <v>376</v>
+        <v>398</v>
       </c>
       <c r="V26" s="9" t="s">
-        <v>302</v>
+        <v>356</v>
       </c>
       <c r="W26" s="9" t="s">
-        <v>377</v>
-      </c>
-      <c r="X26" s="9" t="s">
-        <v>378</v>
-      </c>
-      <c r="Y26" s="16">
-        <v>54576044</v>
-      </c>
-      <c r="Z26" s="17">
-        <v>17491111</v>
-      </c>
-      <c r="AA26" s="18">
-        <v>0.32</v>
-      </c>
-      <c r="AB26" s="18">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="AC26" s="9">
-        <v>103.8</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="16"/>
+      <c r="Z26" s="17"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
       <c r="AD26" s="9" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="27" spans="1:30" ht="31" x14ac:dyDescent="0.35">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30" ht="62" x14ac:dyDescent="0.35">
       <c r="A27" s="9">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C27" s="9" t="s">
         <v>140</v>
@@ -9383,7 +9474,7 @@
         <v>141</v>
       </c>
       <c r="E27" s="11">
-        <v>3.71</v>
+        <v>3.57</v>
       </c>
       <c r="F27" s="11">
         <v>3</v>
@@ -9392,13 +9483,13 @@
         <v>3</v>
       </c>
       <c r="H27" s="11">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="I27" s="11">
         <v>1</v>
       </c>
       <c r="J27" s="11">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="K27" s="11">
         <v>5</v>
@@ -9414,16 +9505,16 @@
         <v>196</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="Q27" s="9" t="s">
-        <v>379</v>
+        <v>401</v>
       </c>
       <c r="R27" s="9" t="s">
-        <v>380</v>
+        <v>402</v>
       </c>
       <c r="S27" s="9" t="s">
-        <v>381</v>
+        <v>403</v>
       </c>
       <c r="T27" s="9" t="s">
         <v>286</v>
@@ -9432,57 +9523,57 @@
         <v>287</v>
       </c>
       <c r="V27" s="9" t="s">
-        <v>250</v>
+        <v>404</v>
       </c>
       <c r="W27" s="9" t="s">
-        <v>382</v>
+        <v>405</v>
       </c>
       <c r="X27" s="9" t="s">
-        <v>383</v>
+        <v>406</v>
       </c>
       <c r="Y27" s="16">
-        <v>25999310</v>
+        <v>17554624</v>
       </c>
       <c r="Z27" s="17">
-        <v>4612764</v>
+        <v>4844770</v>
       </c>
       <c r="AA27" s="18">
-        <v>0.17699999999999999</v>
+        <v>0.27600000000000002</v>
       </c>
       <c r="AB27" s="18">
-        <v>3.1E-2</v>
+        <v>-5.0000000000000001E-3</v>
       </c>
       <c r="AC27" s="9">
-        <v>56.1</v>
+        <v>90.1</v>
       </c>
       <c r="AD27" s="9" t="s">
-        <v>384</v>
+        <v>407</v>
       </c>
     </row>
     <row r="28" spans="1:30" ht="31" x14ac:dyDescent="0.35">
       <c r="A28" s="9">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>140</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E28" s="11">
-        <v>3.66</v>
+        <v>3.52</v>
       </c>
       <c r="F28" s="11">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="G28" s="11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H28" s="11">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="I28" s="11">
         <v>1</v>
@@ -9491,148 +9582,162 @@
         <v>2.5</v>
       </c>
       <c r="K28" s="11">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="L28" s="11">
         <v>3</v>
       </c>
       <c r="M28" s="9"/>
       <c r="N28" s="9" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="O28" s="9" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="P28" s="9" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="Q28" s="9" t="s">
-        <v>385</v>
+        <v>408</v>
       </c>
       <c r="R28" s="9" t="s">
-        <v>386</v>
+        <v>409</v>
       </c>
       <c r="S28" s="9" t="s">
-        <v>387</v>
+        <v>410</v>
       </c>
       <c r="T28" s="9" t="s">
-        <v>388</v>
+        <v>411</v>
       </c>
       <c r="U28" s="9" t="s">
-        <v>389</v>
+        <v>412</v>
       </c>
       <c r="V28" s="9" t="s">
-        <v>390</v>
+        <v>356</v>
       </c>
       <c r="W28" s="9" t="s">
-        <v>391</v>
+        <v>413</v>
       </c>
       <c r="X28" s="9" t="s">
-        <v>392</v>
+        <v>414</v>
       </c>
       <c r="Y28" s="16">
-        <v>7718796</v>
+        <v>30730205</v>
       </c>
       <c r="Z28" s="17">
-        <v>3186892</v>
+        <v>10344879</v>
       </c>
       <c r="AA28" s="18">
-        <v>0.41299999999999998</v>
+        <v>0.33700000000000002</v>
       </c>
       <c r="AB28" s="18">
-        <v>0.14699999999999999</v>
+        <v>6.3E-2</v>
       </c>
       <c r="AC28" s="9">
-        <v>154.69999999999999</v>
+        <v>120.3</v>
       </c>
       <c r="AD28" s="9" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="29" spans="1:30" ht="31" x14ac:dyDescent="0.35">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A29" s="9">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="E29" s="11">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="F29" s="11">
         <v>3</v>
       </c>
       <c r="G29" s="11">
+        <v>5</v>
+      </c>
+      <c r="H29" s="11">
         <v>4</v>
       </c>
-      <c r="H29" s="11">
-        <v>4.5</v>
-      </c>
       <c r="I29" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="11">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="K29" s="11">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="L29" s="11">
-        <v>3</v>
-      </c>
-      <c r="M29" s="9"/>
+        <v>5</v>
+      </c>
+      <c r="M29" s="9">
+        <v>3</v>
+      </c>
       <c r="N29" s="9" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="Q29" s="9" t="s">
-        <v>394</v>
+        <v>214</v>
       </c>
       <c r="R29" s="9" t="s">
-        <v>395</v>
+        <v>215</v>
       </c>
       <c r="S29" s="9" t="s">
-        <v>396</v>
+        <v>216</v>
       </c>
       <c r="T29" s="9" t="s">
-        <v>397</v>
+        <v>217</v>
       </c>
       <c r="U29" s="9" t="s">
-        <v>398</v>
+        <v>218</v>
       </c>
       <c r="V29" s="9" t="s">
-        <v>356</v>
+        <v>219</v>
       </c>
       <c r="W29" s="9" t="s">
-        <v>399</v>
-      </c>
-      <c r="X29" s="9"/>
-      <c r="Y29" s="16"/>
-      <c r="Z29" s="17"/>
-      <c r="AA29" s="9"/>
-      <c r="AB29" s="9"/>
-      <c r="AC29" s="9"/>
+        <v>220</v>
+      </c>
+      <c r="X29" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="Y29" s="16">
+        <v>36774911</v>
+      </c>
+      <c r="Z29" s="17">
+        <v>8769191</v>
+      </c>
+      <c r="AA29" s="18">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="AB29" s="18">
+        <v>-1.4999999999999999E-2</v>
+      </c>
+      <c r="AC29" s="9">
+        <v>79.900000000000006</v>
+      </c>
       <c r="AD29" s="9" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="30" spans="1:30" ht="62" x14ac:dyDescent="0.35">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="30" spans="1:30" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A30" s="9">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>140</v>
@@ -9641,7 +9746,7 @@
         <v>141</v>
       </c>
       <c r="E30" s="11">
-        <v>3.57</v>
+        <v>3.48</v>
       </c>
       <c r="F30" s="11">
         <v>3</v>
@@ -9650,16 +9755,16 @@
         <v>3</v>
       </c>
       <c r="H30" s="11">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="I30" s="11">
         <v>1</v>
       </c>
       <c r="J30" s="11">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="K30" s="11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L30" s="11">
         <v>3</v>
@@ -9675,13 +9780,13 @@
         <v>78</v>
       </c>
       <c r="Q30" s="9" t="s">
-        <v>401</v>
+        <v>416</v>
       </c>
       <c r="R30" s="9" t="s">
-        <v>402</v>
+        <v>417</v>
       </c>
       <c r="S30" s="9" t="s">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="T30" s="9" t="s">
         <v>286</v>
@@ -9690,39 +9795,39 @@
         <v>287</v>
       </c>
       <c r="V30" s="9" t="s">
-        <v>404</v>
+        <v>356</v>
       </c>
       <c r="W30" s="9" t="s">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="X30" s="9" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="Y30" s="16">
-        <v>17554624</v>
+        <v>29436777</v>
       </c>
       <c r="Z30" s="17">
-        <v>4844770</v>
+        <v>5067421</v>
       </c>
       <c r="AA30" s="18">
-        <v>0.27600000000000002</v>
+        <v>0.17199999999999999</v>
       </c>
       <c r="AB30" s="18">
-        <v>-5.0000000000000001E-3</v>
+        <v>-0.02</v>
       </c>
       <c r="AC30" s="9">
-        <v>90.1</v>
+        <v>62.2</v>
       </c>
       <c r="AD30" s="9" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
     </row>
     <row r="31" spans="1:30" ht="31" x14ac:dyDescent="0.35">
       <c r="A31" s="9">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C31" s="9" t="s">
         <v>140</v>
@@ -9731,16 +9836,16 @@
         <v>141</v>
       </c>
       <c r="E31" s="11">
-        <v>3.52</v>
+        <v>3.43</v>
       </c>
       <c r="F31" s="11">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="G31" s="11">
         <v>3</v>
       </c>
       <c r="H31" s="11">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I31" s="11">
         <v>1</v>
@@ -9749,70 +9854,70 @@
         <v>2.5</v>
       </c>
       <c r="K31" s="11">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L31" s="11">
         <v>3</v>
       </c>
       <c r="M31" s="9"/>
       <c r="N31" s="9" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="Q31" s="9" t="s">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="R31" s="9" t="s">
-        <v>409</v>
+        <v>423</v>
       </c>
       <c r="S31" s="9" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="T31" s="9" t="s">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c r="U31" s="9" t="s">
-        <v>412</v>
+        <v>426</v>
       </c>
       <c r="V31" s="9" t="s">
-        <v>356</v>
+        <v>258</v>
       </c>
       <c r="W31" s="9" t="s">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="X31" s="9" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="Y31" s="16">
-        <v>30730205</v>
+        <v>39117557</v>
       </c>
       <c r="Z31" s="17">
-        <v>10344879</v>
+        <v>13988483</v>
       </c>
       <c r="AA31" s="18">
-        <v>0.33700000000000002</v>
+        <v>0.35799999999999998</v>
       </c>
       <c r="AB31" s="18">
-        <v>6.3E-2</v>
+        <v>-4.1000000000000002E-2</v>
       </c>
       <c r="AC31" s="9">
-        <v>120.3</v>
+        <v>132.6</v>
       </c>
       <c r="AD31" s="9" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="32" spans="1:30" ht="46.5" x14ac:dyDescent="0.35">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="32" spans="1:30" ht="31" x14ac:dyDescent="0.35">
       <c r="A32" s="9">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C32" s="9" t="s">
         <v>140</v>
@@ -9821,7 +9926,7 @@
         <v>141</v>
       </c>
       <c r="E32" s="11">
-        <v>3.48</v>
+        <v>3.38</v>
       </c>
       <c r="F32" s="11">
         <v>3</v>
@@ -9830,7 +9935,7 @@
         <v>3</v>
       </c>
       <c r="H32" s="11">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="I32" s="11">
         <v>1</v>
@@ -9839,7 +9944,7 @@
         <v>3.5</v>
       </c>
       <c r="K32" s="11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L32" s="11">
         <v>3</v>
@@ -9852,16 +9957,16 @@
         <v>196</v>
       </c>
       <c r="P32" s="9" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="Q32" s="9" t="s">
-        <v>416</v>
+        <v>429</v>
       </c>
       <c r="R32" s="9" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="S32" s="9" t="s">
-        <v>418</v>
+        <v>431</v>
       </c>
       <c r="T32" s="9" t="s">
         <v>286</v>
@@ -9873,36 +9978,36 @@
         <v>356</v>
       </c>
       <c r="W32" s="9" t="s">
-        <v>419</v>
+        <v>432</v>
       </c>
       <c r="X32" s="9" t="s">
-        <v>420</v>
+        <v>433</v>
       </c>
       <c r="Y32" s="16">
-        <v>29436777</v>
+        <v>20523312</v>
       </c>
       <c r="Z32" s="17">
-        <v>5067421</v>
+        <v>5748239</v>
       </c>
       <c r="AA32" s="18">
-        <v>0.17199999999999999</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="AB32" s="18">
-        <v>-0.02</v>
+        <v>0.08</v>
       </c>
       <c r="AC32" s="9">
-        <v>62.2</v>
+        <v>93</v>
       </c>
       <c r="AD32" s="9" t="s">
-        <v>421</v>
+        <v>179</v>
       </c>
     </row>
     <row r="33" spans="1:30" ht="31" x14ac:dyDescent="0.35">
       <c r="A33" s="9">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C33" s="9" t="s">
         <v>140</v>
@@ -9911,16 +10016,16 @@
         <v>141</v>
       </c>
       <c r="E33" s="11">
-        <v>3.43</v>
+        <v>3.34</v>
       </c>
       <c r="F33" s="11">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="G33" s="11">
         <v>3</v>
       </c>
       <c r="H33" s="11">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="I33" s="11">
         <v>1</v>
@@ -9929,160 +10034,162 @@
         <v>2.5</v>
       </c>
       <c r="K33" s="11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L33" s="11">
         <v>3</v>
       </c>
       <c r="M33" s="9"/>
       <c r="N33" s="9" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="Q33" s="9" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="R33" s="9" t="s">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="S33" s="9" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="T33" s="9" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="U33" s="9" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="V33" s="9" t="s">
-        <v>258</v>
+        <v>439</v>
       </c>
       <c r="W33" s="9" t="s">
-        <v>427</v>
+        <v>440</v>
       </c>
       <c r="X33" s="9" t="s">
-        <v>428</v>
+        <v>441</v>
       </c>
       <c r="Y33" s="16">
-        <v>39117557</v>
+        <v>12874504</v>
       </c>
       <c r="Z33" s="17">
-        <v>13988483</v>
+        <v>2727112</v>
       </c>
       <c r="AA33" s="18">
-        <v>0.35799999999999998</v>
+        <v>0.21199999999999999</v>
       </c>
       <c r="AB33" s="18">
-        <v>-4.1000000000000002E-2</v>
+        <v>-6.9000000000000006E-2</v>
       </c>
       <c r="AC33" s="9">
-        <v>132.6</v>
+        <v>66.3</v>
       </c>
       <c r="AD33" s="9" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="34" spans="1:30" ht="31" x14ac:dyDescent="0.35">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="34" spans="1:30" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A34" s="9">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="E34" s="11">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="F34" s="11">
         <v>3</v>
       </c>
       <c r="G34" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H34" s="11">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="I34" s="11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J34" s="11">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="K34" s="11">
         <v>1</v>
       </c>
       <c r="L34" s="11">
-        <v>3</v>
-      </c>
-      <c r="M34" s="9"/>
+        <v>5</v>
+      </c>
+      <c r="M34" s="9">
+        <v>4</v>
+      </c>
       <c r="N34" s="9" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="O34" s="9" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="P34" s="9" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="Q34" s="9" t="s">
-        <v>429</v>
+        <v>222</v>
       </c>
       <c r="R34" s="9" t="s">
-        <v>430</v>
+        <v>223</v>
       </c>
       <c r="S34" s="9" t="s">
-        <v>431</v>
+        <v>224</v>
       </c>
       <c r="T34" s="9" t="s">
-        <v>286</v>
+        <v>225</v>
       </c>
       <c r="U34" s="9" t="s">
-        <v>287</v>
+        <v>226</v>
       </c>
       <c r="V34" s="9" t="s">
-        <v>356</v>
+        <v>227</v>
       </c>
       <c r="W34" s="9" t="s">
-        <v>432</v>
+        <v>228</v>
       </c>
       <c r="X34" s="9" t="s">
-        <v>433</v>
+        <v>229</v>
       </c>
       <c r="Y34" s="16">
-        <v>20523312</v>
+        <v>34502075</v>
       </c>
       <c r="Z34" s="17">
-        <v>5748239</v>
+        <v>9975811</v>
       </c>
       <c r="AA34" s="18">
-        <v>0.28000000000000003</v>
+        <v>0.28899999999999998</v>
       </c>
       <c r="AB34" s="18">
-        <v>0.08</v>
+        <v>0.13900000000000001</v>
       </c>
       <c r="AC34" s="9">
-        <v>93</v>
+        <v>101.1</v>
       </c>
       <c r="AD34" s="9" t="s">
-        <v>179</v>
+        <v>134</v>
       </c>
     </row>
     <row r="35" spans="1:30" ht="31" x14ac:dyDescent="0.35">
       <c r="A35" s="9">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C35" s="9" t="s">
         <v>140</v>
@@ -10091,16 +10198,16 @@
         <v>141</v>
       </c>
       <c r="E35" s="11">
-        <v>3.34</v>
+        <v>3.29</v>
       </c>
       <c r="F35" s="11">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="G35" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H35" s="11">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="I35" s="11">
         <v>1</v>
@@ -10119,60 +10226,48 @@
         <v>56</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="Q35" s="9" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="R35" s="9" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="S35" s="9" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="T35" s="9" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="U35" s="9" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="V35" s="9" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="W35" s="9" t="s">
-        <v>440</v>
-      </c>
-      <c r="X35" s="9" t="s">
-        <v>441</v>
-      </c>
-      <c r="Y35" s="16">
-        <v>12874504</v>
-      </c>
-      <c r="Z35" s="17">
-        <v>2727112</v>
-      </c>
-      <c r="AA35" s="18">
-        <v>0.21199999999999999</v>
-      </c>
-      <c r="AB35" s="18">
-        <v>-6.9000000000000006E-2</v>
-      </c>
-      <c r="AC35" s="9">
-        <v>66.3</v>
-      </c>
+        <v>449</v>
+      </c>
+      <c r="X35" s="9"/>
+      <c r="Y35" s="16"/>
+      <c r="Z35" s="17"/>
+      <c r="AA35" s="9"/>
+      <c r="AB35" s="9"/>
+      <c r="AC35" s="9"/>
       <c r="AD35" s="9" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
     </row>
     <row r="36" spans="1:30" ht="31" x14ac:dyDescent="0.35">
       <c r="A36" s="9">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C36" s="9" t="s">
         <v>140</v>
@@ -10181,13 +10276,13 @@
         <v>141</v>
       </c>
       <c r="E36" s="11">
-        <v>3.29</v>
+        <v>3.24</v>
       </c>
       <c r="F36" s="11">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="G36" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H36" s="11">
         <v>4</v>
@@ -10199,7 +10294,7 @@
         <v>2.5</v>
       </c>
       <c r="K36" s="11">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="L36" s="11">
         <v>3</v>
@@ -10209,48 +10304,60 @@
         <v>56</v>
       </c>
       <c r="O36" s="9" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="P36" s="9" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="Q36" s="9" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="R36" s="9" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="S36" s="9" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="T36" s="9" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="U36" s="9" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="V36" s="9" t="s">
-        <v>448</v>
+        <v>302</v>
       </c>
       <c r="W36" s="9" t="s">
-        <v>449</v>
-      </c>
-      <c r="X36" s="9"/>
-      <c r="Y36" s="16"/>
-      <c r="Z36" s="17"/>
-      <c r="AA36" s="9"/>
-      <c r="AB36" s="9"/>
-      <c r="AC36" s="9"/>
+        <v>456</v>
+      </c>
+      <c r="X36" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="Y36" s="16">
+        <v>9837710</v>
+      </c>
+      <c r="Z36" s="17">
+        <v>2663549</v>
+      </c>
+      <c r="AA36" s="18">
+        <v>0.27100000000000002</v>
+      </c>
+      <c r="AB36" s="18">
+        <v>2.3E-2</v>
+      </c>
+      <c r="AC36" s="9">
+        <v>85.6</v>
+      </c>
       <c r="AD36" s="9" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
     </row>
     <row r="37" spans="1:30" ht="31" x14ac:dyDescent="0.35">
       <c r="A37" s="9">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C37" s="9" t="s">
         <v>140</v>
@@ -10259,7 +10366,7 @@
         <v>141</v>
       </c>
       <c r="E37" s="11">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="F37" s="11">
         <v>3</v>
@@ -10268,7 +10375,7 @@
         <v>3</v>
       </c>
       <c r="H37" s="11">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="I37" s="11">
         <v>1</v>
@@ -10277,7 +10384,7 @@
         <v>2.5</v>
       </c>
       <c r="K37" s="11">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="L37" s="11">
         <v>3</v>
@@ -10290,75 +10397,75 @@
         <v>213</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="Q37" s="9" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="R37" s="9" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="S37" s="9" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="T37" s="9" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="U37" s="9" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="V37" s="9" t="s">
-        <v>302</v>
+        <v>356</v>
       </c>
       <c r="W37" s="9" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="X37" s="9" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="Y37" s="16">
-        <v>9837710</v>
+        <v>24145050</v>
       </c>
       <c r="Z37" s="17">
-        <v>2663549</v>
+        <v>10543149</v>
       </c>
       <c r="AA37" s="18">
-        <v>0.27100000000000002</v>
+        <v>0.437</v>
       </c>
       <c r="AB37" s="18">
-        <v>2.3E-2</v>
+        <v>-6.5000000000000002E-2</v>
       </c>
       <c r="AC37" s="9">
-        <v>85.6</v>
+        <v>145.6</v>
       </c>
       <c r="AD37" s="9" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="38" spans="1:30" ht="31" x14ac:dyDescent="0.35">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="38" spans="1:30" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A38" s="9">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E38" s="11">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="F38" s="11">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="G38" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H38" s="11">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="I38" s="11">
         <v>1</v>
@@ -10367,70 +10474,70 @@
         <v>2.5</v>
       </c>
       <c r="K38" s="11">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L38" s="11">
         <v>3</v>
       </c>
       <c r="M38" s="9"/>
       <c r="N38" s="9" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="O38" s="9" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="P38" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="Q38" s="9" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="R38" s="9" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="S38" s="9" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="T38" s="9" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="U38" s="9" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="V38" s="9" t="s">
         <v>356</v>
       </c>
       <c r="W38" s="9" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="X38" s="9" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="Y38" s="16">
-        <v>24145050</v>
+        <v>17132291</v>
       </c>
       <c r="Z38" s="17">
-        <v>10543149</v>
+        <v>5130184</v>
       </c>
       <c r="AA38" s="18">
-        <v>0.437</v>
+        <v>0.29899999999999999</v>
       </c>
       <c r="AB38" s="18">
-        <v>-6.5000000000000002E-2</v>
+        <v>-3.2000000000000001E-2</v>
       </c>
       <c r="AC38" s="9">
-        <v>145.6</v>
+        <v>95.6</v>
       </c>
       <c r="AD38" s="9" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="39" spans="1:30" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A39" s="9">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C39" s="9" t="s">
         <v>136</v>
@@ -10439,16 +10546,16 @@
         <v>137</v>
       </c>
       <c r="E39" s="11">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="F39" s="11">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="G39" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H39" s="11">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="I39" s="11">
         <v>1</v>
@@ -10457,88 +10564,88 @@
         <v>2.5</v>
       </c>
       <c r="K39" s="11">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L39" s="11">
         <v>3</v>
       </c>
       <c r="M39" s="9"/>
       <c r="N39" s="9" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="Q39" s="9" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="R39" s="9" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="S39" s="9" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="T39" s="9" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="U39" s="9" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="V39" s="9" t="s">
-        <v>356</v>
+        <v>210</v>
       </c>
       <c r="W39" s="9" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="X39" s="9" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="Y39" s="16">
-        <v>17132291</v>
+        <v>17028139</v>
       </c>
       <c r="Z39" s="17">
-        <v>5130184</v>
+        <v>2071999</v>
       </c>
       <c r="AA39" s="18">
-        <v>0.29899999999999999</v>
+        <v>0.122</v>
       </c>
       <c r="AB39" s="18">
-        <v>-3.2000000000000001E-2</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="AC39" s="9">
-        <v>95.6</v>
+        <v>57.7</v>
       </c>
       <c r="AD39" s="9" t="s">
-        <v>160</v>
+        <v>480</v>
       </c>
     </row>
     <row r="40" spans="1:30" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A40" s="9">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C40" s="9" t="s">
         <v>136</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="E40" s="11">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="F40" s="11">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="G40" s="11">
         <v>2</v>
       </c>
       <c r="H40" s="11">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="I40" s="11">
         <v>1</v>
@@ -10547,70 +10654,70 @@
         <v>2.5</v>
       </c>
       <c r="K40" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L40" s="11">
         <v>3</v>
       </c>
       <c r="M40" s="9"/>
       <c r="N40" s="9" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="O40" s="9" t="s">
         <v>213</v>
       </c>
       <c r="P40" s="9" t="s">
-        <v>69</v>
+        <v>110</v>
       </c>
       <c r="Q40" s="9" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="R40" s="9" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="S40" s="9" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="T40" s="9" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="U40" s="9" t="s">
-        <v>477</v>
+        <v>447</v>
       </c>
       <c r="V40" s="9" t="s">
-        <v>210</v>
+        <v>266</v>
       </c>
       <c r="W40" s="9" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="X40" s="9" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="Y40" s="16">
-        <v>17028139</v>
+        <v>6224198</v>
       </c>
       <c r="Z40" s="17">
-        <v>2071999</v>
+        <v>2185986</v>
       </c>
       <c r="AA40" s="18">
-        <v>0.122</v>
+        <v>0.35099999999999998</v>
       </c>
       <c r="AB40" s="18">
-        <v>1.4999999999999999E-2</v>
+        <v>-5.8999999999999997E-2</v>
       </c>
       <c r="AC40" s="9">
-        <v>57.7</v>
+        <v>146.5</v>
       </c>
       <c r="AD40" s="9" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="41" spans="1:30" ht="46.5" x14ac:dyDescent="0.35">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="41" spans="1:30" ht="31" x14ac:dyDescent="0.35">
       <c r="A41" s="9">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C41" s="9" t="s">
         <v>136</v>
@@ -10619,7 +10726,7 @@
         <v>143</v>
       </c>
       <c r="E41" s="11">
-        <v>3.06</v>
+        <v>3.01</v>
       </c>
       <c r="F41" s="11">
         <v>2.6</v>
@@ -10637,230 +10744,220 @@
         <v>2.5</v>
       </c>
       <c r="K41" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L41" s="11">
         <v>3</v>
       </c>
       <c r="M41" s="9"/>
       <c r="N41" s="9" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="Q41" s="9" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="R41" s="9" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="S41" s="9" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="T41" s="9" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="U41" s="9" t="s">
-        <v>447</v>
+        <v>492</v>
       </c>
       <c r="V41" s="9" t="s">
-        <v>266</v>
+        <v>356</v>
       </c>
       <c r="W41" s="9" t="s">
-        <v>485</v>
-      </c>
-      <c r="X41" s="9" t="s">
-        <v>486</v>
-      </c>
-      <c r="Y41" s="16">
-        <v>6224198</v>
-      </c>
-      <c r="Z41" s="17">
-        <v>2185986</v>
-      </c>
-      <c r="AA41" s="18">
-        <v>0.35099999999999998</v>
-      </c>
-      <c r="AB41" s="18">
-        <v>-5.8999999999999997E-2</v>
-      </c>
-      <c r="AC41" s="9">
-        <v>146.5</v>
-      </c>
+        <v>493</v>
+      </c>
+      <c r="X41" s="9"/>
+      <c r="Y41" s="20"/>
+      <c r="Z41" s="17"/>
+      <c r="AA41" s="9"/>
+      <c r="AB41" s="9"/>
+      <c r="AC41" s="9"/>
       <c r="AD41" s="9" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="42" spans="1:30" ht="31" x14ac:dyDescent="0.35">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="42" spans="1:30" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A42" s="9">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>143</v>
       </c>
       <c r="E42" s="11">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="F42" s="11">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="G42" s="11">
+        <v>4</v>
+      </c>
+      <c r="H42" s="11">
+        <v>4</v>
+      </c>
+      <c r="I42" s="11">
         <v>2</v>
       </c>
-      <c r="H42" s="11">
-        <v>3.8</v>
-      </c>
-      <c r="I42" s="11">
-        <v>1</v>
-      </c>
       <c r="J42" s="11">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="K42" s="11">
+        <v>4</v>
+      </c>
+      <c r="L42" s="11">
         <v>2</v>
-      </c>
-      <c r="L42" s="11">
-        <v>3</v>
       </c>
       <c r="M42" s="9"/>
       <c r="N42" s="9" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="O42" s="9" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="P42" s="9" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="Q42" s="9" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="R42" s="9" t="s">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="S42" s="9" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="T42" s="9" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="U42" s="9" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="V42" s="9" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="W42" s="9" t="s">
-        <v>493</v>
-      </c>
-      <c r="X42" s="9"/>
-      <c r="Y42" s="20"/>
-      <c r="Z42" s="17"/>
-      <c r="AA42" s="9"/>
-      <c r="AB42" s="9"/>
-      <c r="AC42" s="9"/>
+        <v>500</v>
+      </c>
+      <c r="X42" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="Y42" s="16">
+        <v>137153480</v>
+      </c>
+      <c r="Z42" s="17">
+        <v>78811979</v>
+      </c>
+      <c r="AA42" s="18">
+        <v>0.57499999999999996</v>
+      </c>
+      <c r="AB42" s="18">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="AC42" s="9">
+        <v>183.3</v>
+      </c>
       <c r="AD42" s="9" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="43" spans="1:30" ht="46.5" x14ac:dyDescent="0.35">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="43" spans="1:30" ht="31" x14ac:dyDescent="0.35">
       <c r="A43" s="9">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>112</v>
+        <v>64</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="E43" s="11">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="F43" s="11">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="G43" s="11">
         <v>4</v>
       </c>
       <c r="H43" s="11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I43" s="11">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J43" s="11">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="K43" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L43" s="11">
-        <v>2</v>
-      </c>
-      <c r="M43" s="9"/>
+        <v>5</v>
+      </c>
+      <c r="M43" s="9">
+        <v>5</v>
+      </c>
       <c r="N43" s="9" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>113</v>
+        <v>66</v>
       </c>
       <c r="Q43" s="9" t="s">
-        <v>495</v>
+        <v>230</v>
       </c>
       <c r="R43" s="9" t="s">
-        <v>496</v>
+        <v>231</v>
       </c>
       <c r="S43" s="9" t="s">
-        <v>497</v>
+        <v>232</v>
       </c>
       <c r="T43" s="9" t="s">
-        <v>498</v>
+        <v>233</v>
       </c>
       <c r="U43" s="9" t="s">
-        <v>499</v>
+        <v>234</v>
       </c>
       <c r="V43" s="9" t="s">
-        <v>343</v>
+        <v>235</v>
       </c>
       <c r="W43" s="9" t="s">
-        <v>500</v>
-      </c>
-      <c r="X43" s="9" t="s">
-        <v>501</v>
-      </c>
-      <c r="Y43" s="16">
-        <v>137153480</v>
-      </c>
-      <c r="Z43" s="17">
-        <v>78811979</v>
-      </c>
-      <c r="AA43" s="18">
-        <v>0.57499999999999996</v>
-      </c>
-      <c r="AB43" s="18">
-        <v>8.5999999999999993E-2</v>
-      </c>
-      <c r="AC43" s="9">
-        <v>183.3</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="X43" s="9"/>
+      <c r="Y43" s="16"/>
+      <c r="Z43" s="17"/>
+      <c r="AA43" s="9"/>
+      <c r="AB43" s="9"/>
+      <c r="AC43" s="9"/>
       <c r="AD43" s="9" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
     </row>
     <row r="44" spans="1:30" ht="46.5" x14ac:dyDescent="0.35">
@@ -14585,62 +14682,100 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="72.26953125" customWidth="1"/>
-    <col min="2" max="2" width="169.453125" customWidth="1"/>
+    <col min="1" max="1" width="72.26953125" style="25" customWidth="1"/>
+    <col min="2" max="2" width="179.26953125" style="25" customWidth="1"/>
+    <col min="3" max="16384" width="8.6328125" style="25"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="23" t="s">
         <v>765</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="23" t="s">
         <v>766</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="22" t="s">
         <v>767</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="22" t="s">
         <v>768</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="24" t="s">
         <v>769</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="24" t="s">
         <v>770</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="22" t="s">
         <v>771</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="22" t="s">
         <v>772</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="24" t="s">
         <v>773</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="24" t="s">
         <v>774</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="22" t="s">
+        <v>779</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="24" t="s">
+        <v>780</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="31" x14ac:dyDescent="0.35">
+      <c r="A8" s="26" t="s">
+        <v>782</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="31" x14ac:dyDescent="0.35">
+      <c r="A9" s="24" t="s">
         <v>775</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B9" s="24" t="s">
         <v>776</v>
       </c>
     </row>
+    <row r="10" spans="1:2" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="27" t="s">
+        <v>784</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>785</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A6" r:id="rId1" xr:uid="{3F709398-218A-487E-A997-2E960AFDA31B}"/>
+    <hyperlink ref="A7" r:id="rId2" xr:uid="{1CA57D02-E90C-4CE4-B7CA-0F134285E33F}"/>
+    <hyperlink ref="A8" r:id="rId3" location="report-section-overview" xr:uid="{DA8FFCCF-9266-4078-BA8A-88EE07DB2CB7}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
